--- a/forms/app/pregnancy_outcomes.xlsx
+++ b/forms/app/pregnancy_outcomes.xlsx
@@ -13,11 +13,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="581">
   <si>
     <t>list_name</t>
   </si>
   <si>
+    <t xml:space="preserve">form_title </t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
@@ -30,93 +36,87 @@
     <t>choice_filter</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
+    <t>hint::sw</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>repeat_count</t>
+  </si>
+  <si>
+    <t>form_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
     <t>yes_no</t>
   </si>
   <si>
+    <t>path</t>
+  </si>
+  <si>
     <t>yes</t>
   </si>
   <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>media::image::en</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
+    <t>media::image::sw</t>
+  </si>
+  <si>
     <t>Ndiyo</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">form_title </t>
-  </si>
-  <si>
-    <t>form_id</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>appearance</t>
-  </si>
-  <si>
-    <t>read_only</t>
-  </si>
-  <si>
     <t>Pregnancy Outcomes</t>
   </si>
   <si>
-    <t>constraint</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
     <t>Hapana</t>
   </si>
   <si>
-    <t>calculation</t>
-  </si>
-  <si>
-    <t>hint::en</t>
-  </si>
-  <si>
-    <t>hint::sw</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>repeat_count</t>
-  </si>
-  <si>
-    <t>media::image::en</t>
-  </si>
-  <si>
-    <t>media::image::sw</t>
-  </si>
-  <si>
     <t>num_deliveries</t>
   </si>
   <si>
@@ -135,15 +135,60 @@
     <t>More than one</t>
   </si>
   <si>
+    <t>instance::db-doc</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mtoto zaidi ya mmoja </t>
   </si>
   <si>
+    <t>instance::db-doc-ref</t>
+  </si>
+  <si>
     <t>sex</t>
   </si>
   <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
+    <t>./source = 'user'</t>
+  </si>
+  <si>
+    <t>hidden</t>
+  </si>
+  <si>
     <t>pregnancy_outcomes</t>
   </si>
   <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>contact_id</t>
+  </si>
+  <si>
+    <t>Contact ID of the logged in user</t>
+  </si>
+  <si>
+    <t>facility_id</t>
+  </si>
+  <si>
+    <t>Facility ID for the parent user</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
     <t>male</t>
   </si>
   <si>
@@ -153,12 +198,6 @@
     <t>Mwanamme</t>
   </si>
   <si>
-    <t>pages</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
     <t>female</t>
   </si>
   <si>
@@ -168,6 +207,9 @@
     <t>Mwanamke</t>
   </si>
   <si>
+    <t>Name of the logged in user</t>
+  </si>
+  <si>
     <t>delivery_location</t>
   </si>
   <si>
@@ -177,9 +219,15 @@
     <t>Healthcare facility</t>
   </si>
   <si>
+    <t>EDD</t>
+  </si>
+  <si>
     <t>Kituo cha afya</t>
   </si>
   <si>
+    <t>end group</t>
+  </si>
+  <si>
     <t>in_transit</t>
   </si>
   <si>
@@ -189,15 +237,27 @@
     <t>Njiani kueleka kituo cha afya</t>
   </si>
   <si>
+    <t>contact</t>
+  </si>
+  <si>
     <t>home</t>
   </si>
   <si>
     <t>At home / in the community</t>
   </si>
   <si>
+    <t>db:person</t>
+  </si>
+  <si>
     <t>Nyumbani/ ndani ya jamii</t>
   </si>
   <si>
+    <t>_id</t>
+  </si>
+  <si>
+    <t>db-object</t>
+  </si>
+  <si>
     <t>facility_island</t>
   </si>
   <si>
@@ -207,70 +267,34 @@
     <t>Unguja</t>
   </si>
   <si>
-    <t>instance::db-doc</t>
-  </si>
-  <si>
-    <t>instance::db-doc-ref</t>
-  </si>
-  <si>
-    <t>begin group</t>
-  </si>
-  <si>
-    <t>inputs</t>
-  </si>
-  <si>
     <t>pemba</t>
   </si>
   <si>
     <t>Pemba</t>
   </si>
   <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
-    <t>./source = 'user'</t>
-  </si>
-  <si>
-    <t>hidden</t>
-  </si>
-  <si>
     <t>other</t>
   </si>
   <si>
     <t>Other</t>
   </si>
   <si>
-    <t>user</t>
-  </si>
-  <si>
     <t>Sehemu Nyengine</t>
   </si>
   <si>
     <t>facility_district</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>contact_id</t>
-  </si>
-  <si>
     <t>north_a</t>
   </si>
   <si>
-    <t>Contact ID of the logged in user</t>
-  </si>
-  <si>
     <t>North A</t>
   </si>
   <si>
     <t>Kaskazini A</t>
   </si>
   <si>
-    <t>facility_id</t>
-  </si>
-  <si>
-    <t>Facility ID for the parent user</t>
+    <t>date_of_birth</t>
   </si>
   <si>
     <t>north_b</t>
@@ -282,12 +306,18 @@
     <t>Kaskazini B</t>
   </si>
   <si>
+    <t>parent</t>
+  </si>
+  <si>
     <t>central</t>
   </si>
   <si>
     <t>Central</t>
   </si>
   <si>
+    <t>Household UUID</t>
+  </si>
+  <si>
     <t>Wilaya ya kati</t>
   </si>
   <si>
@@ -306,15 +336,9 @@
     <t>West A</t>
   </si>
   <si>
-    <t>Name of the logged in user</t>
-  </si>
-  <si>
     <t>Magharibi A</t>
   </si>
   <si>
-    <t>EDD</t>
-  </si>
-  <si>
     <t>west_b</t>
   </si>
   <si>
@@ -324,34 +348,25 @@
     <t>Magharibi B</t>
   </si>
   <si>
-    <t>end group</t>
-  </si>
-  <si>
     <t>urban</t>
   </si>
   <si>
     <t>Urban</t>
   </si>
   <si>
+    <t>Catchment area UUID</t>
+  </si>
+  <si>
     <t>Mjini</t>
   </si>
   <si>
-    <t>contact</t>
-  </si>
-  <si>
     <t>chakechake</t>
   </si>
   <si>
-    <t>db:person</t>
-  </si>
-  <si>
     <t>Chake Chake</t>
   </si>
   <si>
-    <t>_id</t>
-  </si>
-  <si>
-    <t>db-object</t>
+    <t>Supervisory area UUID</t>
   </si>
   <si>
     <t>micheweni</t>
@@ -372,27 +387,12 @@
     <t>Wete</t>
   </si>
   <si>
+    <t>calculate</t>
+  </si>
+  <si>
     <t>delivery_facility</t>
   </si>
   <si>
-    <t>date_of_birth</t>
-  </si>
-  <si>
-    <t>parent</t>
-  </si>
-  <si>
-    <t>Household UUID</t>
-  </si>
-  <si>
-    <t>Catchment area UUID</t>
-  </si>
-  <si>
-    <t>Supervisory area UUID</t>
-  </si>
-  <si>
-    <t>calculate</t>
-  </si>
-  <si>
     <t>created_by</t>
   </si>
   <si>
@@ -405,141 +405,216 @@
     <t>../inputs/user/contact_id</t>
   </si>
   <si>
+    <t>Chake Chake District Hospital</t>
+  </si>
+  <si>
+    <t>Hospitali ya wilaya ya ChakeChake</t>
+  </si>
+  <si>
     <t>created_by_place_uuid</t>
   </si>
   <si>
-    <t>Chake Chake District Hospital</t>
-  </si>
-  <si>
     <t>../inputs/user/facility_id</t>
   </si>
   <si>
-    <t>Hospitali ya wilaya ya ChakeChake</t>
+    <t>Pujini PHCU+</t>
   </si>
   <si>
     <t>household_uuid</t>
   </si>
   <si>
-    <t>Pujini PHCU+</t>
+    <t>Tundauwa PHCU+</t>
   </si>
   <si>
     <t>../inputs/contact/parent/_id</t>
   </si>
   <si>
-    <t>Tundauwa PHCU+</t>
-  </si>
-  <si>
     <t>Vitongoji PHCC</t>
   </si>
   <si>
     <t>Wesha PHCU+</t>
   </si>
   <si>
+    <t>supervisory_area_uuid</t>
+  </si>
+  <si>
     <t>Konde PHCU+</t>
   </si>
   <si>
-    <t>supervisory_area_uuid</t>
+    <t>../inputs/contact/parent/parent/parent/_id</t>
+  </si>
+  <si>
+    <t>patient_id</t>
   </si>
   <si>
     <t>Makangale PHCU+</t>
   </si>
   <si>
-    <t>../inputs/contact/parent/parent/parent/_id</t>
-  </si>
-  <si>
-    <t>patient_id</t>
+    <t>../inputs/contact/_id</t>
   </si>
   <si>
     <t>Maziwa Ngombe PHCU+</t>
   </si>
   <si>
-    <t>../inputs/contact/_id</t>
+    <t>client_name</t>
+  </si>
+  <si>
+    <t>../inputs/contact/name</t>
   </si>
   <si>
     <t>Micheweni PHCC</t>
   </si>
   <si>
-    <t>client_name</t>
+    <t>client_date_of_birth</t>
+  </si>
+  <si>
+    <t>../inputs/contact/date_of_birth</t>
   </si>
   <si>
     <t>Wingwi PHCU+</t>
   </si>
   <si>
-    <t>../inputs/contact/name</t>
-  </si>
-  <si>
-    <t>client_date_of_birth</t>
+    <t>age_days</t>
+  </si>
+  <si>
+    <t>int(decimal-date-time(now())-decimal-date-time(${client_date_of_birth}))</t>
   </si>
   <si>
     <t>Kiuyu Mbuyuni PHCU+</t>
   </si>
   <si>
-    <t>../inputs/contact/date_of_birth</t>
-  </si>
-  <si>
-    <t>age_days</t>
-  </si>
-  <si>
     <t>Bogoa PHCU+</t>
   </si>
   <si>
-    <t>int(decimal-date-time(now())-decimal-date-time(${client_date_of_birth}))</t>
+    <t>Kengeja PHCU+</t>
   </si>
   <si>
     <t>age_months</t>
   </si>
   <si>
+    <t>Abdallah Mzee District Hospital</t>
+  </si>
+  <si>
+    <t>Hospitali ya wilaya ya Abdalla Mzee</t>
+  </si>
+  <si>
+    <t>Michenzani PHCU+</t>
+  </si>
+  <si>
     <t>int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
   </si>
   <si>
+    <t>Fundo PHCU+</t>
+  </si>
+  <si>
     <t>age_years</t>
   </si>
   <si>
     <t>int(${age_days} div (30 *12),0)</t>
   </si>
   <si>
+    <t>Kojani PHCU+</t>
+  </si>
+  <si>
     <t>age_days_display</t>
   </si>
   <si>
+    <t>Makongeni PHCU+</t>
+  </si>
+  <si>
     <t>${age_days} - (${age_months} * 30) - (${age_years} *12*30)</t>
   </si>
   <si>
+    <t>Wete District Hospital</t>
+  </si>
+  <si>
+    <t>Hospitali ya wilaya ya Wete</t>
+  </si>
+  <si>
+    <t>Mzambarauni PHCU+</t>
+  </si>
+  <si>
     <t>household_head</t>
   </si>
   <si>
+    <t>Junguni PHCU+</t>
+  </si>
+  <si>
     <t>instance('contact-summary')/context/household_head</t>
   </si>
   <si>
     <t>house_number</t>
   </si>
   <si>
+    <t>Ukunjwi PHCU+</t>
+  </si>
+  <si>
     <t>instance('contact-summary')/context/house_number</t>
   </si>
   <si>
     <t>kitongoji</t>
   </si>
   <si>
+    <t>Uondwe PHCU+</t>
+  </si>
+  <si>
     <t>instance('contact-summary')/context/kitongoji</t>
   </si>
   <si>
     <t>phone</t>
   </si>
   <si>
+    <t>Chwaka PHCU+</t>
+  </si>
+  <si>
     <t>instance('contact-summary')/context/phone</t>
   </si>
   <si>
     <t>client_EDD</t>
   </si>
   <si>
+    <t>Mwera PHCU+</t>
+  </si>
+  <si>
+    <t>Unguja Ukuu PHCU+</t>
+  </si>
+  <si>
+    <t>Uzini PHCU+</t>
+  </si>
+  <si>
     <t>today()</t>
   </si>
   <si>
+    <t>Uroa PHCU+</t>
+  </si>
+  <si>
+    <t>Kivunge District Hospital</t>
+  </si>
+  <si>
+    <t>Hospital ya wilaya ya Kivunge</t>
+  </si>
+  <si>
     <t>week</t>
   </si>
   <si>
+    <t>Matemwe PHCU+</t>
+  </si>
+  <si>
+    <t>Nungwi PHCU+</t>
+  </si>
+  <si>
+    <t>Pwani Mchangani PHCU+</t>
+  </si>
+  <si>
     <t>month</t>
   </si>
   <si>
+    <t>Tumbatu Gomani PHCU+</t>
+  </si>
+  <si>
+    <t>Kendwa PHCU+</t>
+  </si>
+  <si>
     <t>client_information</t>
   </si>
   <si>
@@ -549,6 +624,12 @@
     <t>Taarifa za mteja</t>
   </si>
   <si>
+    <t>Bumbwini Misufini PHCU+</t>
+  </si>
+  <si>
+    <t>Donge Vijibweni PHCU+</t>
+  </si>
+  <si>
     <t>field-list</t>
   </si>
   <si>
@@ -558,10 +639,19 @@
     <t>intro_note</t>
   </si>
   <si>
+    <t>Kiongwe PHCU</t>
+  </si>
+  <si>
     <t>Visit type: &lt;span style="font-weight:bold"&gt;Record pregnancy outcome&lt;/span&gt;</t>
   </si>
   <si>
     <t>Aina ya tembeleo: &lt;span style="font-weight:bold"&gt;Kurekodi matokeo ya ujauzito&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Kitope PHCU</t>
+  </si>
+  <si>
+    <t>Mahonda PHCU+</t>
   </si>
   <si>
     <t>household_note</t>
@@ -574,6 +664,9 @@
 Kitongoji: &lt;span style="font-weight:bold"&gt;${kitongoji}&lt;/span&gt;</t>
   </si>
   <si>
+    <t>Jambiani PHCU+</t>
+  </si>
+  <si>
     <t>Jina: &lt;span style=""font-weight:bold""&gt;${client_name}&lt;/span&gt;
 Umri: &lt;span style=""font-weight:bold""&gt;${age_years} miaka, ${age_months} miezi, ${age_days_display} siku&lt;/span&gt;
 Mtu wa karibu kwa mawasiliano: &lt;span style=""font-weight:bold""&gt;${household_head}&lt;/span&gt; 
@@ -590,6 +683,12 @@
     <t>Mawasiliano: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
   </si>
   <si>
+    <t>Makunduchi District Hospital</t>
+  </si>
+  <si>
+    <t>Hospital ya wilaya ya Makunduchi</t>
+  </si>
+  <si>
     <t>confirm_delivery</t>
   </si>
   <si>
@@ -599,6 +698,9 @@
     <t>Mama aliejifungua</t>
   </si>
   <si>
+    <t>Muyuni PHCU+</t>
+  </si>
+  <si>
     <t>select_one pregnancy_outcome</t>
   </si>
   <si>
@@ -608,9 +710,21 @@
     <t xml:space="preserve">What is the outcome of the pregnancy? </t>
   </si>
   <si>
+    <t>Bwejuu PHCU+</t>
+  </si>
+  <si>
+    <t>Chumbuni PHCU+</t>
+  </si>
+  <si>
+    <t>Mnazi Mmoja Hospital</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nini matokeo ya ujauzito? </t>
   </si>
   <si>
+    <t>Hospital ya Mnazimmoja</t>
+  </si>
+  <si>
     <t>date</t>
   </si>
   <si>
@@ -620,6 +734,9 @@
     <t>When did you deliver?</t>
   </si>
   <si>
+    <t>Mwembeladu MCH Clinic</t>
+  </si>
+  <si>
     <t xml:space="preserve">Je umejifungua lini? </t>
   </si>
   <si>
@@ -632,21 +749,36 @@
     <t>Deliveries can be up to 3 months ago</t>
   </si>
   <si>
+    <t>Sebleni PHCU+</t>
+  </si>
+  <si>
     <t>Tarehe ya kujifungua iwe baina ya leo na miezi mitatu nyuma.</t>
   </si>
   <si>
+    <t>Chukwani PHCU+</t>
+  </si>
+  <si>
     <t>pregnancy_loss_note</t>
   </si>
   <si>
     <t>&lt;span style="color:#f58a1f"&gt;Sympathise with the mother for her loss.&lt;/span&gt;</t>
   </si>
   <si>
+    <t>Fuoni PHCU+</t>
+  </si>
+  <si>
     <t>&lt;span style="color:#f58a1f"&gt;Mpe pole mama kwa kuharibika mimba yake.&lt;/span&gt;</t>
   </si>
   <si>
     <t>selected(${pregnancy_outcome},"miscarriage_or_stillbirth")</t>
   </si>
   <si>
+    <t>Kombeni PHCU+</t>
+  </si>
+  <si>
+    <t>Mtofaani PHCU+ (Kinuni)</t>
+  </si>
+  <si>
     <t>date_of_pregnancy_loss</t>
   </si>
   <si>
@@ -656,12 +788,18 @@
     <t>Mimba ya ${client_name} iliharibika lini?</t>
   </si>
   <si>
+    <t>Bumbwisudi PHCU+</t>
+  </si>
+  <si>
     <t>miscarriage_or_stillbirth</t>
   </si>
   <si>
     <t>if((decimal-date-time(${client_EDD}) - decimal-date-time(${date_of_pregnancy_loss})) &gt; (${week} * 12), "miscarriage", "stillbirth")</t>
   </si>
   <si>
+    <t>Selem PHCU+</t>
+  </si>
+  <si>
     <t>delivery_location_assessment</t>
   </si>
   <si>
@@ -671,6 +809,9 @@
     <t>Pahali pa kujifungulia</t>
   </si>
   <si>
+    <t>Nyengine</t>
+  </si>
+  <si>
     <t>select_one delivery_location</t>
   </si>
   <si>
@@ -716,19 +857,43 @@
     <t>Kituo cha afya ulichojifungua kipo katika wilaya gani?</t>
   </si>
   <si>
+    <t>method_facility_delivery</t>
+  </si>
+  <si>
+    <t>normal_vaginal</t>
+  </si>
+  <si>
     <t>selected(${facility_island},"unguja") or selected(${facility_island},"pemba")</t>
   </si>
   <si>
+    <t>Skilled normal vaginal delivery</t>
+  </si>
+  <si>
     <t>choice_filter=${facility_island}</t>
   </si>
   <si>
+    <t>Kujifungua kwa njia ya kawaida kwa msaada mtaalam wa afya</t>
+  </si>
+  <si>
     <t>select_one delivery_facility</t>
   </si>
   <si>
+    <t>caesarian</t>
+  </si>
+  <si>
+    <t>Caesarian section</t>
+  </si>
+  <si>
     <t>Which facility did you deliver in?</t>
   </si>
   <si>
+    <t>Kujifungua kwa njia ya upasuaji.</t>
+  </si>
+  <si>
     <t>Ni kituo gani cha afya ulichojifungulia?</t>
+  </si>
+  <si>
+    <t>vacuum_forceps</t>
   </si>
   <si>
     <t>selected(${facility_district},"north_a") or 
@@ -744,40 +909,118 @@
 selected(${facility_district},"wete")</t>
   </si>
   <si>
+    <t>Vacuum extraction or forceps</t>
+  </si>
+  <si>
     <t>choice_filter=${facility_district}</t>
   </si>
   <si>
+    <t>Kujifungua kwa msaada wa kuvutwa au kutumia vifaa tiba.</t>
+  </si>
+  <si>
     <t>pnc_visit_facility_other</t>
   </si>
   <si>
+    <t>home_delivery_helper</t>
+  </si>
+  <si>
+    <t>traditional_birth_attendant</t>
+  </si>
+  <si>
+    <t>Traditional birth attendant</t>
+  </si>
+  <si>
+    <t>Kujifungua kwa mkunga wa kienyeji/jadi.</t>
+  </si>
+  <si>
+    <t>family_member</t>
+  </si>
+  <si>
     <t>selected(${delivery_facility},"other")</t>
   </si>
   <si>
+    <t>Family member</t>
+  </si>
+  <si>
+    <t>Kwa msaada wa wanafamilia</t>
+  </si>
+  <si>
+    <t>neighbor_friend</t>
+  </si>
+  <si>
+    <t>Neighbor / friend</t>
+  </si>
+  <si>
+    <t>Jirani/Rafika</t>
+  </si>
+  <si>
+    <t>no_one</t>
+  </si>
+  <si>
+    <t>No one</t>
+  </si>
+  <si>
+    <t>Hapana kati ya hizo</t>
+  </si>
+  <si>
+    <t>immediate_cry</t>
+  </si>
+  <si>
+    <t>Yes: Cried immediately, no problem breathing.</t>
+  </si>
+  <si>
     <t>delivery_information</t>
   </si>
   <si>
+    <t>Ndio: Alilia punde tu baada ya kuzaliwa, na hakuwa na tatatizo la kupumua.</t>
+  </si>
+  <si>
     <t>Delivery Information</t>
   </si>
   <si>
     <t>Taarifa za kujifungua.</t>
   </si>
   <si>
+    <t>No: Had difficulty breathing at birth or require resuscitation.</t>
+  </si>
+  <si>
+    <t>Hapana: Alipata tatizo la upumuwaji alipozaliwa au alihitaji msaada wa kidaktari ili aweze kupumua</t>
+  </si>
+  <si>
     <t>select_one method_facility_delivery</t>
   </si>
   <si>
+    <t>major_complications</t>
+  </si>
+  <si>
     <t>facility_delivery_method</t>
   </si>
   <si>
+    <t>antepartum_hemorrhage</t>
+  </si>
+  <si>
     <t>What was the method of delivery?</t>
   </si>
   <si>
+    <t>Antepartum hemorrhage</t>
+  </si>
+  <si>
     <t>Ulijifungua kwa njia gani?</t>
   </si>
   <si>
+    <t xml:space="preserve">Je ulitokwa na damu nyingi kabla ya kujifungua? </t>
+  </si>
+  <si>
+    <t>intrapartum_hemorrhage</t>
+  </si>
+  <si>
+    <t>Intrapartum hemorrhage</t>
+  </si>
+  <si>
     <t>select_one home_delivery_helper</t>
   </si>
   <si>
-    <t>home_delivery_helper</t>
+    <t xml:space="preserve">Je ulitokwa na damu nyingi wakati wa kujifungua? </t>
   </si>
   <si>
     <t>Who was the main person who helped you deliver the baby?</t>
@@ -786,21 +1029,48 @@
     <t>Nani muhusika mkuu aliekusaidia wakati ukimzaa mtoto wako?</t>
   </si>
   <si>
+    <t>postpartum_hemorrhage</t>
+  </si>
+  <si>
+    <t>Postpartum hemorrhage</t>
+  </si>
+  <si>
     <t>not(selected(${delivery_location},"facility"))</t>
   </si>
   <si>
+    <t>Je ulitokwa na damu nyingi baada ya kujifungua?</t>
+  </si>
+  <si>
     <t>select_one yes_no</t>
   </si>
   <si>
+    <t>preeclampsia_eclampsia</t>
+  </si>
+  <si>
     <t>got_facility_pnc</t>
   </si>
   <si>
+    <t>Preeclampsia, eclampsia, or hypertension related</t>
+  </si>
+  <si>
     <t xml:space="preserve">Since the birth of the child, have you and your baby gone to a healthcare facility for postnatal care? </t>
   </si>
   <si>
+    <t>Kifafa cha mimba kabla ya kujifungua, Kifafa cha mimba or pressuere ya kupanda.</t>
+  </si>
+  <si>
     <t>Tokea umzae mtoto wako, wewe na mtoto wako mumesha wahi kwenda kituo cha afya kupata huduma za baada ya kujifungua?</t>
   </si>
   <si>
+    <t>infection</t>
+  </si>
+  <si>
+    <t>Infection (high fever right after delivery)</t>
+  </si>
+  <si>
+    <t>Je ulipata Maambukizi ( Homa kali baada tu ya kujifungua) ?</t>
+  </si>
+  <si>
     <t>got_facility_pnc_note</t>
   </si>
   <si>
@@ -825,46 +1095,97 @@
     <t>selected(${got_facility_pnc},"no")</t>
   </si>
   <si>
+    <t>prolonged_labor</t>
+  </si>
+  <si>
+    <t>Prolonged labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ulipata uchungu wa muda mrefu sana ? </t>
+  </si>
+  <si>
     <t>refer_flag_no_facility_pnc</t>
   </si>
   <si>
+    <t>large_perineal_tear</t>
+  </si>
+  <si>
     <t>if(selected(${got_facility_pnc},"no"),1,0)</t>
   </si>
   <si>
+    <t>Large perineal tear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je mtoto alichana msamba/njia ya uzazi kwa kiasi kikubwa ? </t>
+  </si>
+  <si>
     <t>born_early</t>
   </si>
   <si>
+    <t>retained_placenta</t>
+  </si>
+  <si>
     <t>Was the baby born preterm or too early?</t>
   </si>
   <si>
+    <t>Retained placenta</t>
+  </si>
+  <si>
     <t>Je mtoto alifika muda wake wa kuzaliwa?</t>
   </si>
   <si>
+    <t xml:space="preserve">Je zalio/kondo la nyuma lilichelewa ? </t>
+  </si>
+  <si>
     <t>select_one immediate_cry</t>
   </si>
   <si>
-    <t>immediate_cry</t>
-  </si>
-  <si>
     <t>Did the baby cry immediately after birth?</t>
   </si>
   <si>
+    <t>dont_know</t>
+  </si>
+  <si>
     <t>Je mtoto alilia punde tu baada ya kuzaliwa?</t>
   </si>
   <si>
+    <t>Does not know</t>
+  </si>
+  <si>
+    <t>Sijui</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
     <t>admitted_after_birth</t>
   </si>
   <si>
+    <t>None of the above</t>
+  </si>
+  <si>
     <t>Was baby admitted to neonatal unit/special care area/hospital within the first 24 hours after birth?</t>
   </si>
   <si>
+    <t>Hakuna iliotokezea</t>
+  </si>
+  <si>
     <t>Je, mtoto aliwahi kulazwa hospital katika wodi maalum ya watoto wachanga ndani ya masaa 24 ya mwanzo baada ya kuzaliwa?</t>
   </si>
   <si>
+    <t>how_handled</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>Good/great</t>
+  </si>
+  <si>
     <t>select_multiple major_complications</t>
   </si>
   <si>
-    <t>major_complications</t>
+    <t>Vizuri</t>
   </si>
   <si>
     <t xml:space="preserve">Did the woman experience any of these major medical complications during this delivery? </t>
@@ -873,91 +1194,226 @@
     <t>Je mama alipata matatizo makubwa ya kiafya muda mfupi baada ya kujifungua?</t>
   </si>
   <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somehow good / ok </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afadhali </t>
+  </si>
+  <si>
     <t>(selected(.,"none") and count-selected(.)=1) or (not(selected(.,"none")) and count-selected(.)&gt;=1)</t>
   </si>
   <si>
     <t xml:space="preserve">Cannot select "None of the above" with other options </t>
   </si>
   <si>
+    <t>bad</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>Vibaya</t>
+  </si>
+  <si>
+    <t>why_handled_bad</t>
+  </si>
+  <si>
+    <t>shouted</t>
+  </si>
+  <si>
+    <t>Shouted at</t>
+  </si>
+  <si>
+    <t>Kukaripiwa</t>
+  </si>
+  <si>
+    <t>hit</t>
+  </si>
+  <si>
+    <t>Slapped or hit</t>
+  </si>
+  <si>
     <t>Huwezi kuchaguwa "Hakuna moja wapo" na chaguo jengine</t>
   </si>
   <si>
+    <t>Kupigwa</t>
+  </si>
+  <si>
+    <t>ignored</t>
+  </si>
+  <si>
+    <t>Ignored</t>
+  </si>
+  <si>
+    <t>Kudharauliwa</t>
+  </si>
+  <si>
+    <t>unfriendly</t>
+  </si>
+  <si>
     <t>number_deliveries</t>
   </si>
   <si>
+    <t>People were not friendly</t>
+  </si>
+  <si>
     <t>Number of Deliveries</t>
   </si>
   <si>
+    <t xml:space="preserve">Sio wakarimu </t>
+  </si>
+  <si>
     <t>Idadi ya watoto alioifungua /aliozaa.</t>
   </si>
   <si>
+    <t xml:space="preserve">Nyengine </t>
+  </si>
+  <si>
     <t>select_one num_deliveries</t>
   </si>
   <si>
     <t>check_multiple_deliveries</t>
   </si>
   <si>
+    <t>how_much_paid</t>
+  </si>
+  <si>
     <t>Did you deliver one baby or more than one baby</t>
   </si>
   <si>
+    <t>&lt;1,000</t>
+  </si>
+  <si>
     <t xml:space="preserve">Je umejifungua mtoto mmoja au zaidi ya mtoto mmoja? </t>
   </si>
   <si>
+    <t>Less than one thousand</t>
+  </si>
+  <si>
+    <t>Chini ya Shilingi elfu moja</t>
+  </si>
+  <si>
     <t>integer</t>
   </si>
   <si>
+    <t>1,000 - 10,000</t>
+  </si>
+  <si>
     <t>num_babies_delivered</t>
   </si>
   <si>
+    <t>Between one thousand and ten thousand</t>
+  </si>
+  <si>
     <t>How many babies did you deliver?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kati ya shilingi elfu na shilingi elfu kumi </t>
+  </si>
+  <si>
     <t xml:space="preserve">Je umejifungua watoto wangapi? </t>
   </si>
   <si>
     <t>selected(${check_multiple_deliveries},"more")</t>
   </si>
   <si>
+    <t>10,000 - 20,000</t>
+  </si>
+  <si>
     <t>2 &lt;= . and . &lt;= 4</t>
   </si>
   <si>
+    <t>Between ten thousand and twenty thousand</t>
+  </si>
+  <si>
     <t>Delivery of between 2 and 4 babies is supported</t>
   </si>
   <si>
+    <t>Kati ya shilingi elfu kumi  na shilingi elfu ishirini</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tafadhali ingiza idadi kati ya 2 na 4. </t>
   </si>
   <si>
+    <t>20,000 - 50,000</t>
+  </si>
+  <si>
+    <t>Between twenty thousand and fifty thousand</t>
+  </si>
+  <si>
     <t>live_birth</t>
   </si>
   <si>
+    <t>Kati ya shilingi elfu ishirini na shilingi elfu hamsini</t>
+  </si>
+  <si>
     <t>Is the baby alive?</t>
   </si>
   <si>
     <t xml:space="preserve">Mtoto yuko hai? </t>
   </si>
   <si>
+    <t>&gt;50,000</t>
+  </si>
+  <si>
     <t>selected(${check_multiple_deliveries},"one")</t>
   </si>
   <si>
+    <t>Over fifty thousand</t>
+  </si>
+  <si>
+    <t>Zaidi ya shilingi elfu hamsini</t>
+  </si>
+  <si>
     <t>num_live_births</t>
   </si>
   <si>
+    <t>what_supplies_purchased</t>
+  </si>
+  <si>
     <t>How many of the babies are alive?</t>
   </si>
   <si>
+    <t>gloves</t>
+  </si>
+  <si>
     <t xml:space="preserve">Watoto wangapi wako hai? </t>
   </si>
   <si>
+    <t>Gloves</t>
+  </si>
+  <si>
     <t>0 &lt;= . and . &lt;= ${num_babies_delivered}</t>
   </si>
   <si>
     <t>Enter a number between 0 and the total number of babies delivered</t>
   </si>
   <si>
+    <t>plastic_sheet</t>
+  </si>
+  <si>
     <t>Ingiza nambari baina ya 0 na jumla ya watoto waliozaliwa.</t>
   </si>
   <si>
+    <t>Plastic sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mpira </t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>Medicine</t>
+  </si>
+  <si>
     <t>child_death_count</t>
+  </si>
+  <si>
+    <t>Dawa</t>
   </si>
   <si>
     <t>if(selected(${check_multiple_deliveries},"one") and selected(${live_birth},"yes"),
@@ -967,18 +1423,39 @@
          ${num_babies_delivered} - ${num_live_births}))</t>
   </si>
   <si>
+    <t>cleaning_supplies</t>
+  </si>
+  <si>
+    <t>Cleaning supplies</t>
+  </si>
+  <si>
     <t>child_death_note</t>
   </si>
   <si>
+    <t xml:space="preserve">Vifaa vya kusafishia </t>
+  </si>
+  <si>
+    <t>needles</t>
+  </si>
+  <si>
     <t>I'm very sorry for your loss</t>
   </si>
   <si>
+    <t>Needles/syringe</t>
+  </si>
+  <si>
     <t>Pole sana kwa kupoteza mtoto wako.</t>
   </si>
   <si>
+    <t>Sindano</t>
+  </si>
+  <si>
     <t>${child_death_count} &gt; 0</t>
   </si>
   <si>
+    <t>iv_infusion</t>
+  </si>
+  <si>
     <t>multiple_child_death_note</t>
   </si>
   <si>
@@ -991,6 +1468,12 @@
     <t>${child_death_count} &gt; 1</t>
   </si>
   <si>
+    <t>IV Infusion</t>
+  </si>
+  <si>
+    <t>Dripu</t>
+  </si>
+  <si>
     <t>begin repeat</t>
   </si>
   <si>
@@ -1003,6 +1486,12 @@
     <t>Taarifa za kifo cha mtoto</t>
   </si>
   <si>
+    <t>did_deliver</t>
+  </si>
+  <si>
+    <t>Mother has delivered</t>
+  </si>
+  <si>
     <t>selected(${pregnancy_outcome},"did_deliver") and ${child_death_count} &gt; 0</t>
   </si>
   <si>
@@ -1030,19 +1519,37 @@
     <t>end repeat</t>
   </si>
   <si>
+    <t xml:space="preserve">Mama amejifungua </t>
+  </si>
+  <si>
     <t>child_repeat_count</t>
   </si>
   <si>
+    <t>Mother suffered a miscarriage or stillbirth</t>
+  </si>
+  <si>
     <t>if(selected(${check_multiple_deliveries},"one") and selected(${live_birth},"yes"),1,if(selected(${check_multiple_deliveries},"one") and selected(${live_birth},"no"),0,${num_live_births}))</t>
   </si>
   <si>
+    <t xml:space="preserve">Mimba imeharibika au mtoto kafa tumboni </t>
+  </si>
+  <si>
     <t>intro_data_capture</t>
   </si>
   <si>
+    <t>temp_perm</t>
+  </si>
+  <si>
     <t>Capture Child Data</t>
   </si>
   <si>
+    <t>permanent</t>
+  </si>
+  <si>
     <t>Taarifa za mtoto.</t>
+  </si>
+  <si>
+    <t>Permanent household member - not planning to move elsewhere</t>
   </si>
   <si>
     <t>selected(${pregnancy_outcome},"did_deliver") and ${child_repeat_count} &gt; 0</t>
@@ -1070,42 +1577,39 @@
     <t>child</t>
   </si>
   <si>
+    <t>Mkaazi wa kudumu - Hatohamia sehemu nyengine</t>
+  </si>
+  <si>
     <t>${child_repeat_count}</t>
   </si>
   <si>
     <t>true</t>
   </si>
   <si>
+    <t>temporary</t>
+  </si>
+  <si>
+    <t>Temporary household member - planning to move elsewhere soon</t>
+  </si>
+  <si>
+    <t>Mkaazi wa muda - Atahamia sehemu nyengine</t>
+  </si>
+  <si>
     <t>first_name</t>
   </si>
   <si>
-    <t>Kengeja PHCU+</t>
-  </si>
-  <si>
     <t>What is their first name?</t>
   </si>
   <si>
     <t xml:space="preserve">Ni lipi jina lake la kwanza? </t>
   </si>
   <si>
-    <t>Abdallah Mzee District Hospital</t>
-  </si>
-  <si>
-    <t>Hospitali ya wilaya ya Abdalla Mzee</t>
-  </si>
-  <si>
-    <t>Michenzani PHCU+</t>
-  </si>
-  <si>
     <t>middle_name</t>
   </si>
   <si>
     <t xml:space="preserve">What is their middle name? </t>
   </si>
   <si>
-    <t>Fundo PHCU+</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ni lipi jina la baba yake? </t>
   </si>
   <si>
@@ -1118,31 +1622,28 @@
     <t>Ni lipi jina la babu yake?</t>
   </si>
   <si>
-    <t>Kojani PHCU+</t>
-  </si>
-  <si>
-    <t>Makongeni PHCU+</t>
-  </si>
-  <si>
     <t>concat(${first_name}," ", ${middle_name}," ", ${last_name})</t>
   </si>
   <si>
-    <t>Wete District Hospital</t>
-  </si>
-  <si>
     <t>select_one sex</t>
   </si>
   <si>
-    <t>Hospitali ya wilaya ya Wete</t>
-  </si>
-  <si>
     <t>What is ${first_name}'s sex?</t>
   </si>
   <si>
     <t>Ni ipi jinsia ya ${first_name}?</t>
   </si>
   <si>
-    <t>Mzambarauni PHCU+</t>
+    <t>select_one temp_perm</t>
+  </si>
+  <si>
+    <t>temp_hh_member</t>
+  </si>
+  <si>
+    <t>Does ${first_name} live in this household permanently, or are they here temporarily but later will leave?</t>
+  </si>
+  <si>
+    <t>Je ${first_name} ni mkazi wa kudumu katika nyumba hii  au ni mkazi wa muda tu?</t>
   </si>
   <si>
     <t>${date_of_delivery}</t>
@@ -1154,9 +1655,6 @@
     <t>${child}</t>
   </si>
   <si>
-    <t>Junguni PHCU+</t>
-  </si>
-  <si>
     <t>created_by_doc</t>
   </si>
   <si>
@@ -1166,42 +1664,24 @@
     <t>/pregnancy_outcomes</t>
   </si>
   <si>
-    <t>Ukunjwi PHCU+</t>
-  </si>
-  <si>
     <t>Household</t>
   </si>
   <si>
-    <t>Uondwe PHCU+</t>
-  </si>
-  <si>
     <t>${household_uuid}</t>
   </si>
   <si>
-    <t>Chwaka PHCU+</t>
-  </si>
-  <si>
     <t>Catchment Area</t>
   </si>
   <si>
     <t>${created_by_place_uuid}</t>
   </si>
   <si>
-    <t>Mwera PHCU+</t>
-  </si>
-  <si>
     <t>Supervisory Area</t>
   </si>
   <si>
     <t>${supervisory_area_uuid}</t>
   </si>
   <si>
-    <t>Unguja Ukuu PHCU+</t>
-  </si>
-  <si>
-    <t>Uzini PHCU+</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -1211,39 +1691,18 @@
     <t>person</t>
   </si>
   <si>
-    <t>Uroa PHCU+</t>
-  </si>
-  <si>
-    <t>Kivunge District Hospital</t>
-  </si>
-  <si>
     <t>quality_of_care_survey</t>
   </si>
   <si>
-    <t>Hospital ya wilaya ya Kivunge</t>
-  </si>
-  <si>
     <t>Quality of Care</t>
   </si>
   <si>
     <t>Ubora wa huduma</t>
   </si>
   <si>
-    <t>Matemwe PHCU+</t>
-  </si>
-  <si>
-    <t>Nungwi PHCU+</t>
-  </si>
-  <si>
-    <t>Pwani Mchangani PHCU+</t>
-  </si>
-  <si>
     <t>selected(${pregnancy_outcome},"did_deliver") and ${delivery_location} = "facility"</t>
   </si>
   <si>
-    <t>Tumbatu Gomani PHCU+</t>
-  </si>
-  <si>
     <t>quality_of_care_consent</t>
   </si>
   <si>
@@ -1253,15 +1712,6 @@
     <t>Ningependa kukuuliza maswali machache kuhusu ubora wa huduma ulizopata katika kipindi cha mwisho ulipokwenda kituo cha Afya. Tutapeleka maoni yako bila ya kukutaja jina lako.</t>
   </si>
   <si>
-    <t>Kendwa PHCU+</t>
-  </si>
-  <si>
-    <t>Bumbwini Misufini PHCU+</t>
-  </si>
-  <si>
-    <t>Donge Vijibweni PHCU+</t>
-  </si>
-  <si>
     <t>select_one how_handled</t>
   </si>
   <si>
@@ -1274,9 +1724,6 @@
     <t xml:space="preserve">Ulipokelewa vipi ulipofika kituo cha afya? </t>
   </si>
   <si>
-    <t>Kiongwe PHCU</t>
-  </si>
-  <si>
     <t>selected(${quality_of_care_consent},"yes")</t>
   </si>
   <si>
@@ -1292,9 +1739,6 @@
     <t xml:space="preserve">Kwanini unafikiria ulipokelewa vibaya? </t>
   </si>
   <si>
-    <t>Kitope PHCU</t>
-  </si>
-  <si>
     <t>selected(${quality_of_care_consent},"yes") and selected(${how_handled_facility},"bad")</t>
   </si>
   <si>
@@ -1307,9 +1751,6 @@
     <t xml:space="preserve">Je, ulitakiwa ulipie pesa kwajili ya kujifungua? </t>
   </si>
   <si>
-    <t>Mahonda PHCU+</t>
-  </si>
-  <si>
     <t>purchased_supplies</t>
   </si>
   <si>
@@ -1319,27 +1760,15 @@
     <t xml:space="preserve">Je ulitakiwa kununua kifaa chochote kwajili ya kujifungua? </t>
   </si>
   <si>
-    <t>Jambiani PHCU+</t>
-  </si>
-  <si>
     <t>select_multiple what_supplies_purchased</t>
   </si>
   <si>
-    <t>what_supplies_purchased</t>
-  </si>
-  <si>
     <t>Which supplies did you purchase?</t>
   </si>
   <si>
     <t xml:space="preserve">Ulinunua vifaa gani? </t>
   </si>
   <si>
-    <t>Makunduchi District Hospital</t>
-  </si>
-  <si>
-    <t>Hospital ya wilaya ya Makunduchi</t>
-  </si>
-  <si>
     <t>selected(${quality_of_care_consent},"yes") and selected(${purchased_supplies},"yes")</t>
   </si>
   <si>
@@ -1349,403 +1778,7 @@
     <t>Would you recommend your sister or relative to deliver at the same facility?</t>
   </si>
   <si>
-    <t>Muyuni PHCU+</t>
-  </si>
-  <si>
     <t xml:space="preserve">Je utamshauri dada yako au ndugu yako wa karibu kujifungulia katika kituo hicho? </t>
-  </si>
-  <si>
-    <t>Bwejuu PHCU+</t>
-  </si>
-  <si>
-    <t>Chumbuni PHCU+</t>
-  </si>
-  <si>
-    <t>Mnazi Mmoja Hospital</t>
-  </si>
-  <si>
-    <t>Hospital ya Mnazimmoja</t>
-  </si>
-  <si>
-    <t>Mwembeladu MCH Clinic</t>
-  </si>
-  <si>
-    <t>Sebleni PHCU+</t>
-  </si>
-  <si>
-    <t>Chukwani PHCU+</t>
-  </si>
-  <si>
-    <t>Fuoni PHCU+</t>
-  </si>
-  <si>
-    <t>Kombeni PHCU+</t>
-  </si>
-  <si>
-    <t>Mtofaani PHCU+ (Kinuni)</t>
-  </si>
-  <si>
-    <t>Bumbwisudi PHCU+</t>
-  </si>
-  <si>
-    <t>Selem PHCU+</t>
-  </si>
-  <si>
-    <t>Nyengine</t>
-  </si>
-  <si>
-    <t>method_facility_delivery</t>
-  </si>
-  <si>
-    <t>normal_vaginal</t>
-  </si>
-  <si>
-    <t>Skilled normal vaginal delivery</t>
-  </si>
-  <si>
-    <t>Kujifungua kwa njia ya kawaida kwa msaada mtaalam wa afya</t>
-  </si>
-  <si>
-    <t>caesarian</t>
-  </si>
-  <si>
-    <t>Caesarian section</t>
-  </si>
-  <si>
-    <t>Kujifungua kwa njia ya upasuaji.</t>
-  </si>
-  <si>
-    <t>vacuum_forceps</t>
-  </si>
-  <si>
-    <t>Vacuum extraction or forceps</t>
-  </si>
-  <si>
-    <t>Kujifungua kwa msaada wa kuvutwa au kutumia vifaa tiba.</t>
-  </si>
-  <si>
-    <t>traditional_birth_attendant</t>
-  </si>
-  <si>
-    <t>Traditional birth attendant</t>
-  </si>
-  <si>
-    <t>Kujifungua kwa mkunga wa kienyeji/jadi.</t>
-  </si>
-  <si>
-    <t>family_member</t>
-  </si>
-  <si>
-    <t>Family member</t>
-  </si>
-  <si>
-    <t>Kwa msaada wa wanafamilia</t>
-  </si>
-  <si>
-    <t>neighbor_friend</t>
-  </si>
-  <si>
-    <t>Neighbor / friend</t>
-  </si>
-  <si>
-    <t>Jirani/Rafika</t>
-  </si>
-  <si>
-    <t>no_one</t>
-  </si>
-  <si>
-    <t>No one</t>
-  </si>
-  <si>
-    <t>Hapana kati ya hizo</t>
-  </si>
-  <si>
-    <t>Yes: Cried immediately, no problem breathing.</t>
-  </si>
-  <si>
-    <t>Ndio: Alilia punde tu baada ya kuzaliwa, na hakuwa na tatatizo la kupumua.</t>
-  </si>
-  <si>
-    <t>No: Had difficulty breathing at birth or require resuscitation.</t>
-  </si>
-  <si>
-    <t>Hapana: Alipata tatizo la upumuwaji alipozaliwa au alihitaji msaada wa kidaktari ili aweze kupumua</t>
-  </si>
-  <si>
-    <t>antepartum_hemorrhage</t>
-  </si>
-  <si>
-    <t>Antepartum hemorrhage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je ulitokwa na damu nyingi kabla ya kujifungua? </t>
-  </si>
-  <si>
-    <t>intrapartum_hemorrhage</t>
-  </si>
-  <si>
-    <t>Intrapartum hemorrhage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je ulitokwa na damu nyingi wakati wa kujifungua? </t>
-  </si>
-  <si>
-    <t>postpartum_hemorrhage</t>
-  </si>
-  <si>
-    <t>Postpartum hemorrhage</t>
-  </si>
-  <si>
-    <t>Je ulitokwa na damu nyingi baada ya kujifungua?</t>
-  </si>
-  <si>
-    <t>preeclampsia_eclampsia</t>
-  </si>
-  <si>
-    <t>Preeclampsia, eclampsia, or hypertension related</t>
-  </si>
-  <si>
-    <t>Kifafa cha mimba kabla ya kujifungua, Kifafa cha mimba or pressuere ya kupanda.</t>
-  </si>
-  <si>
-    <t>infection</t>
-  </si>
-  <si>
-    <t>Infection (high fever right after delivery)</t>
-  </si>
-  <si>
-    <t>Je ulipata Maambukizi ( Homa kali baada tu ya kujifungua) ?</t>
-  </si>
-  <si>
-    <t>prolonged_labor</t>
-  </si>
-  <si>
-    <t>Prolonged labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je ulipata uchungu wa muda mrefu sana ? </t>
-  </si>
-  <si>
-    <t>large_perineal_tear</t>
-  </si>
-  <si>
-    <t>Large perineal tear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je mtoto alichana msamba/njia ya uzazi kwa kiasi kikubwa ? </t>
-  </si>
-  <si>
-    <t>retained_placenta</t>
-  </si>
-  <si>
-    <t>Retained placenta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je zalio/kondo la nyuma lilichelewa ? </t>
-  </si>
-  <si>
-    <t>dont_know</t>
-  </si>
-  <si>
-    <t>Does not know</t>
-  </si>
-  <si>
-    <t>Sijui</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>None of the above</t>
-  </si>
-  <si>
-    <t>Hakuna iliotokezea</t>
-  </si>
-  <si>
-    <t>how_handled</t>
-  </si>
-  <si>
-    <t>good</t>
-  </si>
-  <si>
-    <t>Good/great</t>
-  </si>
-  <si>
-    <t>Vizuri</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somehow good / ok </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afadhali </t>
-  </si>
-  <si>
-    <t>bad</t>
-  </si>
-  <si>
-    <t>Bad</t>
-  </si>
-  <si>
-    <t>Vibaya</t>
-  </si>
-  <si>
-    <t>why_handled_bad</t>
-  </si>
-  <si>
-    <t>shouted</t>
-  </si>
-  <si>
-    <t>Shouted at</t>
-  </si>
-  <si>
-    <t>Kukaripiwa</t>
-  </si>
-  <si>
-    <t>hit</t>
-  </si>
-  <si>
-    <t>Slapped or hit</t>
-  </si>
-  <si>
-    <t>Kupigwa</t>
-  </si>
-  <si>
-    <t>ignored</t>
-  </si>
-  <si>
-    <t>Ignored</t>
-  </si>
-  <si>
-    <t>Kudharauliwa</t>
-  </si>
-  <si>
-    <t>unfriendly</t>
-  </si>
-  <si>
-    <t>People were not friendly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sio wakarimu </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nyengine </t>
-  </si>
-  <si>
-    <t>how_much_paid</t>
-  </si>
-  <si>
-    <t>&lt;1,000</t>
-  </si>
-  <si>
-    <t>Less than one thousand</t>
-  </si>
-  <si>
-    <t>Chini ya Shilingi elfu moja</t>
-  </si>
-  <si>
-    <t>1,000 - 10,000</t>
-  </si>
-  <si>
-    <t>Between one thousand and ten thousand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kati ya shilingi elfu na shilingi elfu kumi </t>
-  </si>
-  <si>
-    <t>10,000 - 20,000</t>
-  </si>
-  <si>
-    <t>Between ten thousand and twenty thousand</t>
-  </si>
-  <si>
-    <t>Kati ya shilingi elfu kumi  na shilingi elfu ishirini</t>
-  </si>
-  <si>
-    <t>20,000 - 50,000</t>
-  </si>
-  <si>
-    <t>Between twenty thousand and fifty thousand</t>
-  </si>
-  <si>
-    <t>Kati ya shilingi elfu ishirini na shilingi elfu hamsini</t>
-  </si>
-  <si>
-    <t>&gt;50,000</t>
-  </si>
-  <si>
-    <t>Over fifty thousand</t>
-  </si>
-  <si>
-    <t>Zaidi ya shilingi elfu hamsini</t>
-  </si>
-  <si>
-    <t>gloves</t>
-  </si>
-  <si>
-    <t>Gloves</t>
-  </si>
-  <si>
-    <t>plastic_sheet</t>
-  </si>
-  <si>
-    <t>Plastic sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mpira </t>
-  </si>
-  <si>
-    <t>medicine</t>
-  </si>
-  <si>
-    <t>Medicine</t>
-  </si>
-  <si>
-    <t>Dawa</t>
-  </si>
-  <si>
-    <t>cleaning_supplies</t>
-  </si>
-  <si>
-    <t>Cleaning supplies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vifaa vya kusafishia </t>
-  </si>
-  <si>
-    <t>needles</t>
-  </si>
-  <si>
-    <t>Needles/syringe</t>
-  </si>
-  <si>
-    <t>Sindano</t>
-  </si>
-  <si>
-    <t>iv_infusion</t>
-  </si>
-  <si>
-    <t>IV Infusion</t>
-  </si>
-  <si>
-    <t>Dripu</t>
-  </si>
-  <si>
-    <t>did_deliver</t>
-  </si>
-  <si>
-    <t>Mother has delivered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mama amejifungua </t>
-  </si>
-  <si>
-    <t>Mother suffered a miscarriage or stillbirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mimba imeharibika au mtoto kafa tumboni </t>
   </si>
 </sst>
 </file>
@@ -1788,7 +1821,7 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="10.0"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
     </font>
@@ -1822,7 +1855,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1832,22 +1865,22 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1901,6 +1934,15 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1912,9 +1954,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1953,427 +1992,427 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="T1" s="2" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>81</v>
+        <v>52</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>85</v>
+        <v>54</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>97</v>
+        <v>3</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>70</v>
+      <c r="A7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>121</v>
+      <c r="B22" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="C22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="A25" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
       <c r="L25" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="X25" s="8"/>
+      <c r="Y25" s="8"/>
+      <c r="Z25" s="8"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B26" s="6" t="s">
+      <c r="A26" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
       <c r="L26" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="6"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="6"/>
-      <c r="Z26" s="6"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8"/>
+      <c r="X26" s="8"/>
+      <c r="Y26" s="8"/>
+      <c r="Z26" s="8"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
+      <c r="A27" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
       <c r="L27" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="6"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
+        <v>133</v>
+      </c>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8"/>
+      <c r="X27" s="8"/>
+      <c r="Y27" s="8"/>
+      <c r="Z27" s="8"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>134</v>
+      <c r="A28" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -2385,15 +2424,15 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>141</v>
+      <c r="A29" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -2405,15 +2444,15 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -2424,16 +2463,16 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="7" t="s">
-        <v>146</v>
+      <c r="L30" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>148</v>
+        <v>124</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -2444,16 +2483,16 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-      <c r="L31" s="7" t="s">
-        <v>150</v>
+      <c r="L31" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>151</v>
+        <v>124</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -2464,16 +2503,16 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-      <c r="L32" s="7" t="s">
-        <v>153</v>
+      <c r="L32" s="3" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -2485,15 +2524,15 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -2504,16 +2543,16 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="7" t="s">
-        <v>158</v>
+      <c r="L34" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -2524,16 +2563,16 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="7" t="s">
-        <v>160</v>
+      <c r="L35" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -2544,16 +2583,16 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="7" t="s">
-        <v>162</v>
+      <c r="L36" s="3" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -2565,15 +2604,15 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="15" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -2585,15 +2624,15 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="15" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -2605,15 +2644,15 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="15" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -2625,15 +2664,15 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="15" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>171</v>
+      <c r="A41" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="1"/>
@@ -2645,7 +2684,7 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="17" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
@@ -2664,10 +2703,10 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="1"/>
@@ -2698,10 +2737,10 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="1"/>
@@ -2732,229 +2771,229 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>176</v>
+        <v>200</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>181</v>
+        <v>207</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>209</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>184</v>
+        <v>213</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>188</v>
+        <v>218</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="K51" s="22" t="s">
-        <v>203</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>207</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>207</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>211</v>
+        <v>256</v>
       </c>
       <c r="C54" s="2"/>
       <c r="L54" s="2" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="C55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="Q56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>218</v>
+        <v>265</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -2962,44 +3001,44 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>219</v>
+        <v>266</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>220</v>
+        <v>267</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="G58" s="2"/>
       <c r="Q58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" s="23" t="s">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="G59" s="16"/>
       <c r="H59" s="1"/>
@@ -3024,72 +3063,72 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>229</v>
+        <v>276</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>230</v>
+        <v>277</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="G60" s="2"/>
       <c r="M60" s="2" t="s">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="Q60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>233</v>
+        <v>284</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>236</v>
+        <v>291</v>
       </c>
       <c r="G61" s="2"/>
       <c r="M61" s="2" t="s">
-        <v>237</v>
+        <v>293</v>
       </c>
       <c r="Q61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" s="23" t="s">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>239</v>
+        <v>301</v>
       </c>
       <c r="G62" s="16"/>
       <c r="H62" s="1"/>
@@ -3114,10 +3153,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="C63" s="2"/>
       <c r="F63" s="2"/>
@@ -3126,157 +3165,157 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>240</v>
+        <v>312</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>241</v>
+        <v>314</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>242</v>
+        <v>315</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="G64" s="2"/>
       <c r="Q64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>243</v>
+        <v>318</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>244</v>
+        <v>320</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>245</v>
+        <v>322</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>246</v>
+        <v>324</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="G65" s="2"/>
       <c r="Q65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>247</v>
+        <v>328</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>249</v>
+        <v>330</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>250</v>
+        <v>331</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>251</v>
+        <v>334</v>
       </c>
       <c r="G66" s="2"/>
       <c r="Q66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>253</v>
+        <v>338</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>254</v>
+        <v>340</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>255</v>
+        <v>342</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>251</v>
+        <v>334</v>
       </c>
       <c r="G67" s="2"/>
       <c r="Q67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>256</v>
+        <v>346</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>257</v>
+        <v>347</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>258</v>
+        <v>348</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>259</v>
+        <v>349</v>
       </c>
       <c r="G68" s="2"/>
       <c r="Q68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>261</v>
+        <v>351</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>262</v>
+        <v>352</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>263</v>
+        <v>353</v>
       </c>
       <c r="G69" s="2"/>
       <c r="Q69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>264</v>
+        <v>357</v>
       </c>
       <c r="C70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="L70" s="2" t="s">
-        <v>265</v>
+        <v>359</v>
       </c>
       <c r="Q70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>266</v>
+        <v>362</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>267</v>
+        <v>364</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>268</v>
+        <v>366</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -3284,19 +3323,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>269</v>
+        <v>368</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>271</v>
+        <v>369</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>272</v>
+        <v>371</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -3304,19 +3343,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>273</v>
+        <v>375</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>274</v>
+        <v>377</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>275</v>
+        <v>379</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -3324,39 +3363,39 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>276</v>
+        <v>383</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>278</v>
+        <v>385</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>279</v>
+        <v>386</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="I74" s="20" t="s">
-        <v>280</v>
+        <v>390</v>
       </c>
       <c r="J74" s="25" t="s">
-        <v>281</v>
+        <v>391</v>
       </c>
       <c r="K74" s="25" t="s">
-        <v>282</v>
+        <v>401</v>
       </c>
       <c r="Q74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>240</v>
+        <v>312</v>
       </c>
       <c r="C75" s="2"/>
       <c r="F75" s="2"/>
@@ -3365,153 +3404,153 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>283</v>
+        <v>407</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>284</v>
+        <v>409</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>285</v>
+        <v>411</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>286</v>
+        <v>413</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>287</v>
+        <v>414</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>288</v>
+        <v>416</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>289</v>
+        <v>418</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>290</v>
+        <v>421</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>291</v>
+        <v>423</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>292</v>
+        <v>425</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>293</v>
+        <v>427</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>294</v>
+        <v>428</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>295</v>
+        <v>430</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>296</v>
+        <v>432</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>297</v>
+        <v>434</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>298</v>
+        <v>437</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>299</v>
+        <v>439</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>301</v>
+        <v>442</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>290</v>
+        <v>421</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>302</v>
+        <v>445</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>303</v>
+        <v>447</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>304</v>
+        <v>449</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>294</v>
+        <v>428</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>305</v>
+        <v>451</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>306</v>
+        <v>452</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>307</v>
+        <v>454</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>283</v>
+        <v>407</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>308</v>
+        <v>459</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>309</v>
+        <v>461</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>310</v>
+        <v>464</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>311</v>
+        <v>467</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>312</v>
+        <v>469</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>313</v>
+        <v>471</v>
       </c>
       <c r="G83" s="2"/>
       <c r="L83" s="2"/>
@@ -3519,19 +3558,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>314</v>
+        <v>473</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>315</v>
+        <v>474</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>316</v>
+        <v>475</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>317</v>
+        <v>476</v>
       </c>
       <c r="G84" s="2"/>
       <c r="L84" s="2"/>
@@ -3539,597 +3578,615 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>318</v>
+        <v>479</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>319</v>
+        <v>480</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>320</v>
+        <v>481</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>321</v>
+        <v>482</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>322</v>
+        <v>485</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="L85" s="2"/>
       <c r="Q85" s="2" t="s">
-        <v>323</v>
+        <v>486</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>324</v>
+        <v>487</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>325</v>
+        <v>488</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>327</v>
+        <v>490</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>328</v>
+        <v>491</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>329</v>
+        <v>492</v>
       </c>
       <c r="L86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>330</v>
+        <v>493</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>319</v>
+        <v>480</v>
       </c>
       <c r="L87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>331</v>
+        <v>495</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>332</v>
+        <v>497</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>333</v>
+        <v>499</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>334</v>
+        <v>501</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>335</v>
+        <v>503</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>336</v>
+        <v>505</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="Q89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>337</v>
+        <v>506</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>338</v>
+        <v>507</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>339</v>
+        <v>508</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>301</v>
+        <v>442</v>
       </c>
       <c r="Q90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>340</v>
+        <v>509</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>341</v>
+        <v>510</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>342</v>
+        <v>511</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>294</v>
+        <v>428</v>
       </c>
       <c r="Q91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>318</v>
+        <v>479</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>343</v>
+        <v>512</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="T92" s="26" t="s">
-        <v>345</v>
+        <v>514</v>
+      </c>
+      <c r="T92" s="29" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>346</v>
+      <c r="A93" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>519</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>348</v>
+        <v>520</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>6</v>
+        <v>521</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="B94" s="27" t="s">
-        <v>353</v>
+      <c r="A94" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="B94" s="30" t="s">
+        <v>522</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>354</v>
+        <v>523</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>6</v>
+        <v>524</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="B95" s="27" t="s">
-        <v>357</v>
+      <c r="A95" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="B95" s="30" t="s">
+        <v>525</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>358</v>
+        <v>526</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>6</v>
+        <v>527</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="B96" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
+      <c r="A96" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B96" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
       <c r="L96" s="24" t="s">
-        <v>362</v>
+        <v>528</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>364</v>
+        <v>529</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>366</v>
+        <v>530</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>367</v>
+        <v>531</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>369</v>
-      </c>
+      <c r="A98" s="23" t="s">
+        <v>532</v>
+      </c>
+      <c r="B98" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="C98" s="24" t="s">
+        <v>534</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>370</v>
+        <v>93</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="U99" s="2" t="s">
-        <v>371</v>
+        <v>536</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>373</v>
+        <v>537</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>374</v>
+        <v>538</v>
       </c>
       <c r="U100" s="2" t="s">
-        <v>375</v>
+        <v>538</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>70</v>
+        <v>539</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="U101" s="2" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="L102" s="2" t="s">
-        <v>379</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>70</v>
+        <v>542</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="L104" s="2" t="s">
-        <v>382</v>
+        <v>46</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>70</v>
+        <v>544</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>385</v>
+        <v>46</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>121</v>
+        <v>79</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="L110" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="P110" s="2" t="s">
-        <v>390</v>
+        <v>97</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>330</v>
+        <v>124</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>343</v>
+        <v>2</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>103</v>
+        <v>493</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>333</v>
+        <v>512</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D113" s="28" t="s">
-        <v>396</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="G113" s="2"/>
-      <c r="Q113" s="2"/>
+        <v>499</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>252</v>
+        <v>44</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>402</v>
+        <v>551</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D114" s="29" t="s">
-        <v>404</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F114" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="D114" s="31" t="s">
+        <v>553</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>554</v>
+      </c>
       <c r="G114" s="2"/>
       <c r="Q114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>408</v>
+        <v>336</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>409</v>
+        <v>555</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>411</v>
+        <v>556</v>
+      </c>
+      <c r="D115" s="32" t="s">
+        <v>557</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>413</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="Q115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>414</v>
+        <v>558</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>415</v>
+        <v>559</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>416</v>
+        <v>560</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>417</v>
+        <v>561</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>419</v>
+        <v>562</v>
       </c>
       <c r="G116" s="2"/>
       <c r="Q116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>252</v>
+        <v>563</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>420</v>
+        <v>564</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>421</v>
+        <v>565</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>422</v>
+        <v>566</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>413</v>
+        <v>567</v>
       </c>
       <c r="G117" s="2"/>
       <c r="Q117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>424</v>
+        <v>568</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>425</v>
+        <v>569</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>426</v>
+        <v>570</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>413</v>
+        <v>562</v>
       </c>
       <c r="G118" s="2"/>
       <c r="Q118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>428</v>
+        <v>336</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>429</v>
+        <v>571</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>430</v>
+        <v>572</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>431</v>
+        <v>573</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>434</v>
+        <v>562</v>
       </c>
       <c r="G119" s="2"/>
       <c r="Q119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>252</v>
+        <v>574</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>436</v>
+        <v>575</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>438</v>
+        <v>576</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>413</v>
+        <v>577</v>
       </c>
       <c r="G120" s="2"/>
       <c r="Q120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>103</v>
+        <v>336</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="F121" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>562</v>
+      </c>
       <c r="G121" s="2"/>
       <c r="Q121" s="2"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="Q122" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -4154,30 +4211,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -4204,16 +4261,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -4263,365 +4320,365 @@
         <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>45</v>
+      <c r="B6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>50</v>
+      <c r="A7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" ref="B25:B88" si="1">lower(substitute(C25," ",""))</f>
         <v>chakechakedistricthospital</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
         <v>pujiniphcu+</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
         <v>tundauwaphcu+</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
@@ -4634,12 +4691,12 @@
         <v>138</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
@@ -4652,1671 +4709,1699 @@
         <v>139</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
         <v>kondephcu+</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
         <v>makangalephcu+</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
         <v>maziwangombephcu+</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
         <v>micheweniphcc</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
         <v>wingwiphcu+</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
         <v>kiuyumbuyuniphcu+</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
         <v>bogoaphcu+</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
         <v>kengejaphcu+</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>347</v>
+        <v>157</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>347</v>
+        <v>157</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
         <v>abdallahmzeedistricthospital</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>350</v>
+        <v>159</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>351</v>
+        <v>160</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
         <v>michenzaniphcu+</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>352</v>
+        <v>161</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>352</v>
+        <v>161</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
         <v>fundophcu+</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>355</v>
+        <v>163</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>355</v>
+        <v>163</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
         <v>kojaniphcu+</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>360</v>
+        <v>166</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>360</v>
+        <v>166</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
         <v>makongeniphcu+</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>361</v>
+        <v>168</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>361</v>
+        <v>168</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
         <v>wetedistricthospital</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>363</v>
+        <v>170</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>365</v>
+        <v>171</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
         <v>mzambarauniphcu+</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>368</v>
+        <v>172</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>368</v>
+        <v>172</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
         <v>junguniphcu+</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>372</v>
+        <v>174</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>372</v>
+        <v>174</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
         <v>ukunjwiphcu+</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>376</v>
+        <v>177</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>376</v>
+        <v>177</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
         <v>uondwephcu+</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>378</v>
+        <v>180</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>378</v>
+        <v>180</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
         <v>chwakaphcu+</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>380</v>
+        <v>183</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>380</v>
+        <v>183</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
         <v>mweraphcu+</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>383</v>
+        <v>186</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>383</v>
+        <v>186</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
         <v>ungujaukuuphcu+</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>386</v>
+        <v>187</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>386</v>
+        <v>187</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
         <v>uziniphcu+</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>387</v>
+        <v>188</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>387</v>
+        <v>188</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
         <v>uroaphcu+</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>391</v>
+        <v>190</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>391</v>
+        <v>190</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
         <v>kivungedistricthospital</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>392</v>
+        <v>191</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>394</v>
+        <v>192</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
         <v>matemwephcu+</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>397</v>
+        <v>194</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>397</v>
+        <v>194</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
         <v>nungwiphcu+</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>398</v>
+        <v>195</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>398</v>
+        <v>195</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
         <v>pwanimchanganiphcu+</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>399</v>
+        <v>196</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>399</v>
+        <v>196</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
         <v>tumbatugomaniphcu+</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>401</v>
+        <v>198</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>401</v>
+        <v>198</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
         <v>kendwaphcu+</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>405</v>
+        <v>199</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>405</v>
+        <v>199</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
         <v>bumbwinimisufiniphcu+</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>406</v>
+        <v>203</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>406</v>
+        <v>203</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
         <v>dongevijibweniphcu+</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>407</v>
+        <v>204</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>407</v>
+        <v>204</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
         <v>kiongwephcu</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>412</v>
+        <v>208</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>412</v>
+        <v>208</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
         <v>kitopephcu</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>418</v>
+        <v>211</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>418</v>
+        <v>211</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
         <v>mahondaphcu+</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>423</v>
+        <v>212</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>423</v>
+        <v>212</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
         <v>jambianiphcu+</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>427</v>
+        <v>215</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>427</v>
+        <v>215</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
         <v>makunduchidistricthospital</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>432</v>
+        <v>220</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>433</v>
+        <v>221</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
         <v>muyuniphcu+</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>437</v>
+        <v>225</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>437</v>
+        <v>225</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
         <v>bwejuuphcu+</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>439</v>
+        <v>229</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>439</v>
+        <v>229</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" si="1"/>
         <v>chumbuniphcu+</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="1"/>
         <v>mnazimmojahospital</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>441</v>
+        <v>231</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>442</v>
+        <v>233</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="1"/>
         <v>mwembeladumchclinic</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>443</v>
+        <v>237</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>443</v>
+        <v>237</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="1"/>
         <v>sebleniphcu+</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>444</v>
+        <v>242</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>444</v>
+        <v>242</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="1"/>
         <v>chukwaniphcu+</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="1"/>
         <v>fuoniphcu+</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>446</v>
+        <v>247</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>446</v>
+        <v>247</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="1"/>
         <v>kombeniphcu+</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>447</v>
+        <v>250</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>447</v>
+        <v>250</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="1"/>
         <v>mtofaaniphcu+(kinuni)</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>448</v>
+        <v>251</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>448</v>
+        <v>251</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="1"/>
         <v>bumbwisudiphcu+</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>449</v>
+        <v>255</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>449</v>
+        <v>255</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="1"/>
         <v>selemphcu+</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>450</v>
+        <v>258</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>450</v>
+        <v>258</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E78" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E79" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E80" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E81" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E82" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E83" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E84" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E85" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E86" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E87" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="E88" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>452</v>
+        <v>278</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>453</v>
+        <v>279</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>454</v>
+        <v>281</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>455</v>
+        <v>283</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>452</v>
+        <v>278</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>456</v>
+        <v>285</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>457</v>
+        <v>286</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>458</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>452</v>
+        <v>278</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>459</v>
+        <v>290</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>460</v>
+        <v>292</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>461</v>
+        <v>294</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>462</v>
+        <v>297</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>463</v>
+        <v>298</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>464</v>
+        <v>299</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>465</v>
+        <v>300</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>466</v>
+        <v>302</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>467</v>
+        <v>303</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>468</v>
+        <v>304</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>469</v>
+        <v>305</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>470</v>
+        <v>306</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>471</v>
+        <v>307</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>472</v>
+        <v>308</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>473</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>474</v>
+        <v>311</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>475</v>
+        <v>313</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>476</v>
+        <v>316</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>477</v>
+        <v>317</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>478</v>
+        <v>321</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>479</v>
+        <v>323</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>480</v>
+        <v>325</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>481</v>
+        <v>326</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>482</v>
+        <v>327</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>483</v>
+        <v>329</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>484</v>
+        <v>332</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>485</v>
+        <v>333</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>486</v>
+        <v>335</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>487</v>
+        <v>337</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>488</v>
+        <v>339</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>489</v>
+        <v>341</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>490</v>
+        <v>343</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>491</v>
+        <v>344</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>492</v>
+        <v>345</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>493</v>
+        <v>354</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>494</v>
+        <v>355</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>495</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>496</v>
+        <v>358</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>497</v>
+        <v>360</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>498</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>499</v>
+        <v>363</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>500</v>
+        <v>365</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>501</v>
+        <v>367</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>502</v>
+        <v>370</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>503</v>
+        <v>372</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>504</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>505</v>
+        <v>374</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>506</v>
+        <v>376</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>507</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>508</v>
+        <v>380</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>509</v>
+        <v>381</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>510</v>
+        <v>382</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>511</v>
+        <v>384</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>508</v>
+        <v>380</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>512</v>
+        <v>387</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>513</v>
+        <v>388</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>514</v>
+        <v>389</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>508</v>
+        <v>380</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>515</v>
+        <v>392</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>516</v>
+        <v>393</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>517</v>
+        <v>394</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>518</v>
+        <v>395</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>519</v>
+        <v>396</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>520</v>
+        <v>397</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>521</v>
+        <v>398</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>518</v>
+        <v>395</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>522</v>
+        <v>399</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>523</v>
+        <v>400</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>524</v>
+        <v>402</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>518</v>
+        <v>395</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>525</v>
+        <v>403</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>526</v>
+        <v>404</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>527</v>
+        <v>405</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>518</v>
+        <v>395</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>528</v>
+        <v>406</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>529</v>
+        <v>408</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>530</v>
+        <v>410</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>518</v>
+        <v>395</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>531</v>
+        <v>412</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>532</v>
+        <v>415</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>533</v>
+        <v>417</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>534</v>
+        <v>419</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>535</v>
+        <v>420</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>532</v>
+        <v>415</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>536</v>
+        <v>422</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>537</v>
+        <v>424</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>538</v>
+        <v>426</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>532</v>
+        <v>415</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>539</v>
+        <v>429</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>540</v>
+        <v>431</v>
       </c>
       <c r="D120" s="20" t="s">
-        <v>541</v>
+        <v>433</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>532</v>
+        <v>415</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>542</v>
+        <v>435</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>543</v>
+        <v>436</v>
       </c>
       <c r="D121" s="20" t="s">
-        <v>544</v>
+        <v>438</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>532</v>
+        <v>415</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>545</v>
+        <v>441</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>546</v>
+        <v>443</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>547</v>
+        <v>444</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>548</v>
+        <v>448</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>549</v>
+        <v>450</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>549</v>
+        <v>450</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>550</v>
+        <v>453</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>551</v>
+        <v>455</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>552</v>
+        <v>456</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>553</v>
+        <v>457</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>554</v>
+        <v>458</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>555</v>
+        <v>460</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>556</v>
+        <v>462</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>557</v>
+        <v>463</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>558</v>
+        <v>465</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>559</v>
+        <v>466</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>560</v>
+        <v>468</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>561</v>
+        <v>470</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>562</v>
+        <v>472</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>563</v>
+        <v>477</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>564</v>
+        <v>478</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="C130" s="30" t="s">
-        <v>566</v>
+        <v>483</v>
+      </c>
+      <c r="C130" s="26" t="s">
+        <v>484</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>567</v>
+        <v>494</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>211</v>
+        <v>256</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>568</v>
+        <v>496</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>569</v>
+        <v>498</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="B132" s="14" t="s">
+        <v>502</v>
+      </c>
+      <c r="C132" s="27" t="s">
+        <v>504</v>
+      </c>
+      <c r="D132" s="28" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="B133" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="C133" s="27" t="s">
+        <v>517</v>
+      </c>
+      <c r="D133" s="28" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -6337,39 +6422,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>42</v>
+      <c r="A2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C2" s="5">
         <v>43580.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1"/>
     </row>

--- a/forms/app/pregnancy_outcomes.xlsx
+++ b/forms/app/pregnancy_outcomes.xlsx
@@ -13,53 +13,53 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="592">
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>label::en</t>
+  </si>
+  <si>
+    <t>label::sw</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">form_title </t>
+  </si>
   <si>
     <t>list_name</t>
   </si>
   <si>
-    <t xml:space="preserve">form_title </t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>label::en</t>
-  </si>
-  <si>
-    <t>label::sw</t>
-  </si>
-  <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>appearance</t>
-  </si>
-  <si>
-    <t>read_only</t>
-  </si>
-  <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
-    <t>calculation</t>
-  </si>
-  <si>
     <t>hint::en</t>
   </si>
   <si>
@@ -72,6 +72,12 @@
     <t>repeat_count</t>
   </si>
   <si>
+    <t>media::image::en</t>
+  </si>
+  <si>
+    <t>media::image::sw</t>
+  </si>
+  <si>
     <t>form_id</t>
   </si>
   <si>
@@ -81,31 +87,73 @@
     <t>style</t>
   </si>
   <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>Pregnancy Outcomes</t>
+  </si>
+  <si>
+    <t>instance::db-doc</t>
+  </si>
+  <si>
+    <t>instance::db-doc-ref</t>
+  </si>
+  <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
+    <t>./source = 'user'</t>
+  </si>
+  <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>pregnancy_outcomes</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>contact_id</t>
+  </si>
+  <si>
+    <t>Contact ID of the logged in user</t>
+  </si>
+  <si>
     <t>yes_no</t>
   </si>
   <si>
-    <t>path</t>
+    <t>facility_id</t>
   </si>
   <si>
     <t>yes</t>
   </si>
   <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>media::image::en</t>
+    <t>Facility ID for the parent user</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>media::image::sw</t>
+    <t>pages</t>
   </si>
   <si>
     <t>Ndiyo</t>
   </si>
   <si>
-    <t>Pregnancy Outcomes</t>
+    <t>data</t>
   </si>
   <si>
     <t>no</t>
@@ -117,6 +165,15 @@
     <t>Hapana</t>
   </si>
   <si>
+    <t>Name of the logged in user</t>
+  </si>
+  <si>
+    <t>EDD</t>
+  </si>
+  <si>
+    <t>end group</t>
+  </si>
+  <si>
     <t>num_deliveries</t>
   </si>
   <si>
@@ -129,64 +186,40 @@
     <t>Mtoto mmoja</t>
   </si>
   <si>
+    <t>contact</t>
+  </si>
+  <si>
     <t>more</t>
   </si>
   <si>
+    <t>db:person</t>
+  </si>
+  <si>
     <t>More than one</t>
   </si>
   <si>
-    <t>instance::db-doc</t>
+    <t>_id</t>
   </si>
   <si>
     <t xml:space="preserve">Mtoto zaidi ya mmoja </t>
   </si>
   <si>
-    <t>instance::db-doc-ref</t>
+    <t>db-object</t>
   </si>
   <si>
     <t>sex</t>
   </si>
   <si>
-    <t>begin group</t>
-  </si>
-  <si>
-    <t>inputs</t>
-  </si>
-  <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
-    <t>./source = 'user'</t>
-  </si>
-  <si>
-    <t>hidden</t>
-  </si>
-  <si>
-    <t>pregnancy_outcomes</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>contact_id</t>
-  </si>
-  <si>
-    <t>Contact ID of the logged in user</t>
-  </si>
-  <si>
-    <t>facility_id</t>
-  </si>
-  <si>
-    <t>Facility ID for the parent user</t>
-  </si>
-  <si>
-    <t>pages</t>
-  </si>
-  <si>
-    <t>data</t>
+    <t>date_of_birth</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>Household UUID</t>
+  </si>
+  <si>
+    <t>Catchment area UUID</t>
   </si>
   <si>
     <t>male</t>
@@ -195,6 +228,9 @@
     <t>Male</t>
   </si>
   <si>
+    <t>Supervisory area UUID</t>
+  </si>
+  <si>
     <t>Mwanamme</t>
   </si>
   <si>
@@ -204,12 +240,12 @@
     <t>Female</t>
   </si>
   <si>
+    <t>calculate</t>
+  </si>
+  <si>
     <t>Mwanamke</t>
   </si>
   <si>
-    <t>Name of the logged in user</t>
-  </si>
-  <si>
     <t>delivery_location</t>
   </si>
   <si>
@@ -219,15 +255,9 @@
     <t>Healthcare facility</t>
   </si>
   <si>
-    <t>EDD</t>
-  </si>
-  <si>
     <t>Kituo cha afya</t>
   </si>
   <si>
-    <t>end group</t>
-  </si>
-  <si>
     <t>in_transit</t>
   </si>
   <si>
@@ -237,27 +267,15 @@
     <t>Njiani kueleka kituo cha afya</t>
   </si>
   <si>
-    <t>contact</t>
-  </si>
-  <si>
     <t>home</t>
   </si>
   <si>
     <t>At home / in the community</t>
   </si>
   <si>
-    <t>db:person</t>
-  </si>
-  <si>
     <t>Nyumbani/ ndani ya jamii</t>
   </si>
   <si>
-    <t>_id</t>
-  </si>
-  <si>
-    <t>db-object</t>
-  </si>
-  <si>
     <t>facility_island</t>
   </si>
   <si>
@@ -273,6 +291,9 @@
     <t>Pemba</t>
   </si>
   <si>
+    <t>../inputs/user/name</t>
+  </si>
+  <si>
     <t>other</t>
   </si>
   <si>
@@ -294,9 +315,6 @@
     <t>Kaskazini A</t>
   </si>
   <si>
-    <t>date_of_birth</t>
-  </si>
-  <si>
     <t>north_b</t>
   </si>
   <si>
@@ -306,18 +324,12 @@
     <t>Kaskazini B</t>
   </si>
   <si>
-    <t>parent</t>
-  </si>
-  <si>
     <t>central</t>
   </si>
   <si>
     <t>Central</t>
   </si>
   <si>
-    <t>Household UUID</t>
-  </si>
-  <si>
     <t>Wilaya ya kati</t>
   </si>
   <si>
@@ -330,6 +342,9 @@
     <t>Wilaya ya kusini</t>
   </si>
   <si>
+    <t>../inputs/user/contact_id</t>
+  </si>
+  <si>
     <t>west_a</t>
   </si>
   <si>
@@ -348,25 +363,28 @@
     <t>Magharibi B</t>
   </si>
   <si>
+    <t xml:space="preserve">facility_id </t>
+  </si>
+  <si>
     <t>urban</t>
   </si>
   <si>
     <t>Urban</t>
   </si>
   <si>
-    <t>Catchment area UUID</t>
-  </si>
-  <si>
     <t>Mjini</t>
   </si>
   <si>
+    <t>../inputs/user/facility_id</t>
+  </si>
+  <si>
     <t>chakechake</t>
   </si>
   <si>
     <t>Chake Chake</t>
   </si>
   <si>
-    <t>Supervisory area UUID</t>
+    <t>household_uuid</t>
   </si>
   <si>
     <t>micheweni</t>
@@ -375,6 +393,9 @@
     <t>Micheweni</t>
   </si>
   <si>
+    <t>../inputs/contact/parent/_id</t>
+  </si>
+  <si>
     <t>mkoani</t>
   </si>
   <si>
@@ -387,22 +408,40 @@
     <t>Wete</t>
   </si>
   <si>
-    <t>calculate</t>
-  </si>
-  <si>
     <t>delivery_facility</t>
   </si>
   <si>
-    <t>created_by</t>
-  </si>
-  <si>
-    <t>../inputs/user/name</t>
-  </si>
-  <si>
-    <t>created_by_person_uuid</t>
-  </si>
-  <si>
-    <t>../inputs/user/contact_id</t>
+    <t>supervisory_area_uuid</t>
+  </si>
+  <si>
+    <t>../inputs/contact/parent/parent/parent/_id</t>
+  </si>
+  <si>
+    <t>patient_id</t>
+  </si>
+  <si>
+    <t>../inputs/contact/_id</t>
+  </si>
+  <si>
+    <t>client_name</t>
+  </si>
+  <si>
+    <t>../inputs/contact/name</t>
+  </si>
+  <si>
+    <t>client_date_of_birth</t>
+  </si>
+  <si>
+    <t>../inputs/contact/date_of_birth</t>
+  </si>
+  <si>
+    <t>age_days</t>
+  </si>
+  <si>
+    <t>int(decimal-date-time(now())-decimal-date-time(${client_date_of_birth}))</t>
+  </si>
+  <si>
+    <t>age_months</t>
   </si>
   <si>
     <t>Chake Chake District Hospital</t>
@@ -411,73 +450,76 @@
     <t>Hospitali ya wilaya ya ChakeChake</t>
   </si>
   <si>
-    <t>created_by_place_uuid</t>
-  </si>
-  <si>
-    <t>../inputs/user/facility_id</t>
+    <t>int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
+  </si>
+  <si>
+    <t>age_years</t>
+  </si>
+  <si>
+    <t>int(${age_days} div (30 *12),0)</t>
+  </si>
+  <si>
+    <t>age_days_display</t>
+  </si>
+  <si>
+    <t>${age_days} - (${age_months} * 30) - (${age_years} *12*30)</t>
+  </si>
+  <si>
+    <t>household_head</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/household_head</t>
   </si>
   <si>
     <t>Pujini PHCU+</t>
   </si>
   <si>
-    <t>household_uuid</t>
-  </si>
-  <si>
     <t>Tundauwa PHCU+</t>
   </si>
   <si>
-    <t>../inputs/contact/parent/_id</t>
-  </si>
-  <si>
     <t>Vitongoji PHCC</t>
   </si>
   <si>
+    <t>house_number</t>
+  </si>
+  <si>
     <t>Wesha PHCU+</t>
   </si>
   <si>
-    <t>supervisory_area_uuid</t>
+    <t>instance('contact-summary')/context/house_number</t>
   </si>
   <si>
     <t>Konde PHCU+</t>
   </si>
   <si>
-    <t>../inputs/contact/parent/parent/parent/_id</t>
-  </si>
-  <si>
-    <t>patient_id</t>
+    <t>kitongoji</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/kitongoji</t>
   </si>
   <si>
     <t>Makangale PHCU+</t>
   </si>
   <si>
-    <t>../inputs/contact/_id</t>
+    <t>phone</t>
   </si>
   <si>
     <t>Maziwa Ngombe PHCU+</t>
   </si>
   <si>
-    <t>client_name</t>
-  </si>
-  <si>
-    <t>../inputs/contact/name</t>
+    <t>instance('contact-summary')/context/phone</t>
+  </si>
+  <si>
+    <t>client_EDD</t>
   </si>
   <si>
     <t>Micheweni PHCC</t>
   </si>
   <si>
-    <t>client_date_of_birth</t>
-  </si>
-  <si>
-    <t>../inputs/contact/date_of_birth</t>
-  </si>
-  <si>
     <t>Wingwi PHCU+</t>
   </si>
   <si>
-    <t>age_days</t>
-  </si>
-  <si>
-    <t>int(decimal-date-time(now())-decimal-date-time(${client_date_of_birth}))</t>
+    <t>today()</t>
   </si>
   <si>
     <t>Kiuyu Mbuyuni PHCU+</t>
@@ -489,7 +531,7 @@
     <t>Kengeja PHCU+</t>
   </si>
   <si>
-    <t>age_months</t>
+    <t>week</t>
   </si>
   <si>
     <t>Abdallah Mzee District Hospital</t>
@@ -501,30 +543,18 @@
     <t>Michenzani PHCU+</t>
   </si>
   <si>
-    <t>int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
-  </si>
-  <si>
     <t>Fundo PHCU+</t>
   </si>
   <si>
-    <t>age_years</t>
-  </si>
-  <si>
-    <t>int(${age_days} div (30 *12),0)</t>
-  </si>
-  <si>
     <t>Kojani PHCU+</t>
   </si>
   <si>
-    <t>age_days_display</t>
+    <t>month</t>
   </si>
   <si>
     <t>Makongeni PHCU+</t>
   </si>
   <si>
-    <t>${age_days} - (${age_months} * 30) - (${age_years} *12*30)</t>
-  </si>
-  <si>
     <t>Wete District Hospital</t>
   </si>
   <si>
@@ -534,57 +564,39 @@
     <t>Mzambarauni PHCU+</t>
   </si>
   <si>
-    <t>household_head</t>
+    <t xml:space="preserve">begin group </t>
   </si>
   <si>
     <t>Junguni PHCU+</t>
   </si>
   <si>
-    <t>instance('contact-summary')/context/household_head</t>
-  </si>
-  <si>
-    <t>house_number</t>
-  </si>
-  <si>
     <t>Ukunjwi PHCU+</t>
   </si>
   <si>
-    <t>instance('contact-summary')/context/house_number</t>
-  </si>
-  <si>
-    <t>kitongoji</t>
-  </si>
-  <si>
     <t>Uondwe PHCU+</t>
   </si>
   <si>
-    <t>instance('contact-summary')/context/kitongoji</t>
-  </si>
-  <si>
-    <t>phone</t>
+    <t>covid19_intro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precautionary measures when visiting a client  </t>
   </si>
   <si>
     <t>Chwaka PHCU+</t>
   </si>
   <si>
-    <t>instance('contact-summary')/context/phone</t>
-  </si>
-  <si>
-    <t>client_EDD</t>
-  </si>
-  <si>
     <t>Mwera PHCU+</t>
   </si>
   <si>
+    <t>Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
+  </si>
+  <si>
     <t>Unguja Ukuu PHCU+</t>
   </si>
   <si>
     <t>Uzini PHCU+</t>
   </si>
   <si>
-    <t>today()</t>
-  </si>
-  <si>
     <t>Uroa PHCU+</t>
   </si>
   <si>
@@ -594,19 +606,44 @@
     <t>Hospital ya wilaya ya Kivunge</t>
   </si>
   <si>
-    <t>week</t>
-  </si>
-  <si>
     <t>Matemwe PHCU+</t>
   </si>
   <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>covid19_intro_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;As a CHV, you are responsible for making sure that you are providing the community with health education and services while trying to take precautions to stop the transmission of Corona virus to one another. Therefore, make sure you consider the following while you conduct the visits:  
+•        Wash your hands with soap/sanitizer as many time as you can while at home, once you are at the client’s house and when you leave.
+•        Keep a 2 meters distance while talking to your clients.
+•        Don’t shake hands with your clients. 
+•        Avoid group gatherings.
+•        Provide the service at the open space and if it should be inside, make sure the windows and doors are open. 
+•        Cover your mouth with a towel or elbow when you sneeze or cough. 
+•        Do not go for a visit if you have symptoms of fever, cough or frequent sneezing.&lt;/span&gt; 
+</t>
+  </si>
+  <si>
     <t>Nungwi PHCU+</t>
   </si>
   <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Kama mhudumu wa afya ya jamii, una jukumu la kuhakikisha unatoa elimu ya afya ya jamii na huduma huku ukijikinga ili kuepusha kusambaa kwa maambukizi ya korona kutoka kwa mtu mmoja kwenda kwa mwengine. Hivyo hakikisha unazingatia yafuatayo wakati ukiwa unatoa huduma:
+•        Osha mikono yako kwa maji na sabuni au kutumia vitakasa mikono mara nyingi kadiri unavyoweza ukiwa nyumbani kwako,nyumbani kwa mteja wako na pindi ukimaliza kutoa huduma. 
+•        Hakikisha kuna umbali wa mita mbili kati yako na mteja wako unayeenda kumtembelea 
+•        Pindi ukiongea na wateja wako , usishikane mikono. 
+•        Epuka mikusanyiko. 
+•        Toa huduma katika maeneo yaliyo wazi na ikitokea ukafanya ndani hakikisha milango na madirisha yanakuwa wazi.  
+•        Funika mdomo wako kwa kitambaa au kiwiko unavyooenda chafya au kukohoa. 
+•        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; 
+</t>
+  </si>
+  <si>
     <t>Pwani Mchangani PHCU+</t>
   </si>
   <si>
-    <t>month</t>
+    <t xml:space="preserve">end group </t>
   </si>
   <si>
     <t>Tumbatu Gomani PHCU+</t>
@@ -615,6 +652,12 @@
     <t>Kendwa PHCU+</t>
   </si>
   <si>
+    <t>Bumbwini Misufini PHCU+</t>
+  </si>
+  <si>
+    <t>Donge Vijibweni PHCU+</t>
+  </si>
+  <si>
     <t>client_information</t>
   </si>
   <si>
@@ -624,34 +667,55 @@
     <t>Taarifa za mteja</t>
   </si>
   <si>
-    <t>Bumbwini Misufini PHCU+</t>
-  </si>
-  <si>
-    <t>Donge Vijibweni PHCU+</t>
+    <t>Kiongwe PHCU</t>
+  </si>
+  <si>
+    <t>Kitope PHCU</t>
+  </si>
+  <si>
+    <t>Mahonda PHCU+</t>
+  </si>
+  <si>
+    <t>Jambiani PHCU+</t>
   </si>
   <si>
     <t>field-list</t>
   </si>
   <si>
-    <t>note</t>
+    <t>Makunduchi District Hospital</t>
+  </si>
+  <si>
+    <t>Hospital ya wilaya ya Makunduchi</t>
   </si>
   <si>
     <t>intro_note</t>
   </si>
   <si>
-    <t>Kiongwe PHCU</t>
-  </si>
-  <si>
     <t>Visit type: &lt;span style="font-weight:bold"&gt;Record pregnancy outcome&lt;/span&gt;</t>
   </si>
   <si>
+    <t>Muyuni PHCU+</t>
+  </si>
+  <si>
     <t>Aina ya tembeleo: &lt;span style="font-weight:bold"&gt;Kurekodi matokeo ya ujauzito&lt;/span&gt;</t>
   </si>
   <si>
-    <t>Kitope PHCU</t>
-  </si>
-  <si>
-    <t>Mahonda PHCU+</t>
+    <t>Bwejuu PHCU+</t>
+  </si>
+  <si>
+    <t>Chumbuni PHCU+</t>
+  </si>
+  <si>
+    <t>Mnazi Mmoja Hospital</t>
+  </si>
+  <si>
+    <t>Hospital ya Mnazimmoja</t>
+  </si>
+  <si>
+    <t>Mwembeladu MCH Clinic</t>
+  </si>
+  <si>
+    <t>Sebleni PHCU+</t>
   </si>
   <si>
     <t>household_note</t>
@@ -664,7 +728,7 @@
 Kitongoji: &lt;span style="font-weight:bold"&gt;${kitongoji}&lt;/span&gt;</t>
   </si>
   <si>
-    <t>Jambiani PHCU+</t>
+    <t>Chukwani PHCU+</t>
   </si>
   <si>
     <t>Jina: &lt;span style=""font-weight:bold""&gt;${client_name}&lt;/span&gt;
@@ -674,6 +738,9 @@
 Kitongoji: &lt;span style=""font-weight:bold""&gt;${kitongoji}&lt;/span&gt;</t>
   </si>
   <si>
+    <t>Fuoni PHCU+</t>
+  </si>
+  <si>
     <t>phone_note</t>
   </si>
   <si>
@@ -683,10 +750,10 @@
     <t>Mawasiliano: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
   </si>
   <si>
-    <t>Makunduchi District Hospital</t>
-  </si>
-  <si>
-    <t>Hospital ya wilaya ya Makunduchi</t>
+    <t>Kombeni PHCU+</t>
+  </si>
+  <si>
+    <t>Mtofaani PHCU+ (Kinuni)</t>
   </si>
   <si>
     <t>confirm_delivery</t>
@@ -698,7 +765,7 @@
     <t>Mama aliejifungua</t>
   </si>
   <si>
-    <t>Muyuni PHCU+</t>
+    <t>Bumbwisudi PHCU+</t>
   </si>
   <si>
     <t>select_one pregnancy_outcome</t>
@@ -707,24 +774,18 @@
     <t>pregnancy_outcome</t>
   </si>
   <si>
+    <t>Selem PHCU+</t>
+  </si>
+  <si>
     <t xml:space="preserve">What is the outcome of the pregnancy? </t>
   </si>
   <si>
-    <t>Bwejuu PHCU+</t>
-  </si>
-  <si>
-    <t>Chumbuni PHCU+</t>
-  </si>
-  <si>
-    <t>Mnazi Mmoja Hospital</t>
+    <t>Nyengine</t>
   </si>
   <si>
     <t xml:space="preserve">Nini matokeo ya ujauzito? </t>
   </si>
   <si>
-    <t>Hospital ya Mnazimmoja</t>
-  </si>
-  <si>
     <t>date</t>
   </si>
   <si>
@@ -734,9 +795,6 @@
     <t>When did you deliver?</t>
   </si>
   <si>
-    <t>Mwembeladu MCH Clinic</t>
-  </si>
-  <si>
     <t xml:space="preserve">Je umejifungua lini? </t>
   </si>
   <si>
@@ -749,46 +807,40 @@
     <t>Deliveries can be up to 3 months ago</t>
   </si>
   <si>
-    <t>Sebleni PHCU+</t>
-  </si>
-  <si>
     <t>Tarehe ya kujifungua iwe baina ya leo na miezi mitatu nyuma.</t>
   </si>
   <si>
-    <t>Chukwani PHCU+</t>
-  </si>
-  <si>
     <t>pregnancy_loss_note</t>
   </si>
   <si>
     <t>&lt;span style="color:#f58a1f"&gt;Sympathise with the mother for her loss.&lt;/span&gt;</t>
   </si>
   <si>
-    <t>Fuoni PHCU+</t>
-  </si>
-  <si>
     <t>&lt;span style="color:#f58a1f"&gt;Mpe pole mama kwa kuharibika mimba yake.&lt;/span&gt;</t>
   </si>
   <si>
     <t>selected(${pregnancy_outcome},"miscarriage_or_stillbirth")</t>
   </si>
   <si>
-    <t>Kombeni PHCU+</t>
-  </si>
-  <si>
-    <t>Mtofaani PHCU+ (Kinuni)</t>
-  </si>
-  <si>
     <t>date_of_pregnancy_loss</t>
   </si>
   <si>
     <t>When did ${client_name} lose the pregnancy?</t>
   </si>
   <si>
+    <t>method_facility_delivery</t>
+  </si>
+  <si>
     <t>Mimba ya ${client_name} iliharibika lini?</t>
   </si>
   <si>
-    <t>Bumbwisudi PHCU+</t>
+    <t>normal_vaginal</t>
+  </si>
+  <si>
+    <t>Skilled normal vaginal delivery</t>
+  </si>
+  <si>
+    <t>Kujifungua kwa njia ya kawaida kwa msaada mtaalam wa afya</t>
   </si>
   <si>
     <t>miscarriage_or_stillbirth</t>
@@ -797,48 +849,108 @@
     <t>if((decimal-date-time(${client_EDD}) - decimal-date-time(${date_of_pregnancy_loss})) &gt; (${week} * 12), "miscarriage", "stillbirth")</t>
   </si>
   <si>
-    <t>Selem PHCU+</t>
+    <t>caesarian</t>
+  </si>
+  <si>
+    <t>Caesarian section</t>
+  </si>
+  <si>
+    <t>Kujifungua kwa njia ya upasuaji.</t>
+  </si>
+  <si>
+    <t>vacuum_forceps</t>
   </si>
   <si>
     <t>delivery_location_assessment</t>
   </si>
   <si>
+    <t>Vacuum extraction or forceps</t>
+  </si>
+  <si>
     <t>Delivery Location</t>
   </si>
   <si>
+    <t>Kujifungua kwa msaada wa kuvutwa au kutumia vifaa tiba.</t>
+  </si>
+  <si>
     <t>Pahali pa kujifungulia</t>
   </si>
   <si>
-    <t>Nyengine</t>
+    <t>home_delivery_helper</t>
+  </si>
+  <si>
+    <t>traditional_birth_attendant</t>
+  </si>
+  <si>
+    <t>Traditional birth attendant</t>
   </si>
   <si>
     <t>select_one delivery_location</t>
   </si>
   <si>
+    <t>Kujifungua kwa mkunga wa kienyeji/jadi.</t>
+  </si>
+  <si>
     <t>Where did you deliver?</t>
   </si>
   <si>
     <t xml:space="preserve">Wapi umejifungua? </t>
   </si>
   <si>
+    <t>family_member</t>
+  </si>
+  <si>
+    <t>Family member</t>
+  </si>
+  <si>
     <t>select_one facility_island</t>
   </si>
   <si>
+    <t>Kwa msaada wa wanafamilia</t>
+  </si>
+  <si>
     <t>Did you deliver in a facility in Unguja or Pemba?</t>
   </si>
   <si>
     <t xml:space="preserve">Ulijifungua katika kituo cha afya kilichopo Unguja au Pemba? </t>
   </si>
   <si>
+    <t>neighbor_friend</t>
+  </si>
+  <si>
     <t>selected(${delivery_location},"facility")</t>
   </si>
   <si>
+    <t>Neighbor / friend</t>
+  </si>
+  <si>
+    <t>Jirani/Rafika</t>
+  </si>
+  <si>
     <t>text</t>
   </si>
   <si>
+    <t>no_one</t>
+  </si>
+  <si>
+    <t>No one</t>
+  </si>
+  <si>
+    <t>Hapana kati ya hizo</t>
+  </si>
+  <si>
+    <t>immediate_cry</t>
+  </si>
+  <si>
+    <t>Yes: Cried immediately, no problem breathing.</t>
+  </si>
+  <si>
     <t>pnc_visit_island_other</t>
   </si>
   <si>
+    <t>Ndio: Alilia punde tu baada ya kuzaliwa, na hakuwa na tatatizo la kupumua.</t>
+  </si>
+  <si>
     <t>Please specify</t>
   </si>
   <si>
@@ -848,52 +960,67 @@
     <t>selected(${facility_island},"other")</t>
   </si>
   <si>
+    <t>No: Had difficulty breathing at birth or require resuscitation.</t>
+  </si>
+  <si>
+    <t>Hapana: Alipata tatizo la upumuwaji alipozaliwa au alihitaji msaada wa kidaktari ili aweze kupumua</t>
+  </si>
+  <si>
+    <t>major_complications</t>
+  </si>
+  <si>
+    <t>antepartum_hemorrhage</t>
+  </si>
+  <si>
+    <t>Antepartum hemorrhage</t>
+  </si>
+  <si>
     <t>select_one facility_district</t>
   </si>
   <si>
+    <t xml:space="preserve">Je ulitokwa na damu nyingi kabla ya kujifungua? </t>
+  </si>
+  <si>
     <t>What district was the facility in?</t>
   </si>
   <si>
     <t>Kituo cha afya ulichojifungua kipo katika wilaya gani?</t>
   </si>
   <si>
-    <t>method_facility_delivery</t>
-  </si>
-  <si>
-    <t>normal_vaginal</t>
+    <t>intrapartum_hemorrhage</t>
+  </si>
+  <si>
+    <t>Intrapartum hemorrhage</t>
   </si>
   <si>
     <t>selected(${facility_island},"unguja") or selected(${facility_island},"pemba")</t>
   </si>
   <si>
-    <t>Skilled normal vaginal delivery</t>
+    <t xml:space="preserve">Je ulitokwa na damu nyingi wakati wa kujifungua? </t>
   </si>
   <si>
     <t>choice_filter=${facility_island}</t>
   </si>
   <si>
-    <t>Kujifungua kwa njia ya kawaida kwa msaada mtaalam wa afya</t>
+    <t>postpartum_hemorrhage</t>
   </si>
   <si>
     <t>select_one delivery_facility</t>
   </si>
   <si>
-    <t>caesarian</t>
-  </si>
-  <si>
-    <t>Caesarian section</t>
+    <t>Postpartum hemorrhage</t>
   </si>
   <si>
     <t>Which facility did you deliver in?</t>
   </si>
   <si>
-    <t>Kujifungua kwa njia ya upasuaji.</t>
+    <t>Je ulitokwa na damu nyingi baada ya kujifungua?</t>
   </si>
   <si>
     <t>Ni kituo gani cha afya ulichojifungulia?</t>
   </si>
   <si>
-    <t>vacuum_forceps</t>
+    <t>preeclampsia_eclampsia</t>
   </si>
   <si>
     <t>selected(${facility_district},"north_a") or 
@@ -909,171 +1036,192 @@
 selected(${facility_district},"wete")</t>
   </si>
   <si>
-    <t>Vacuum extraction or forceps</t>
+    <t>Preeclampsia, eclampsia, or hypertension related</t>
   </si>
   <si>
     <t>choice_filter=${facility_district}</t>
   </si>
   <si>
-    <t>Kujifungua kwa msaada wa kuvutwa au kutumia vifaa tiba.</t>
+    <t>Kifafa cha mimba kabla ya kujifungua, Kifafa cha mimba or pressuere ya kupanda.</t>
   </si>
   <si>
     <t>pnc_visit_facility_other</t>
   </si>
   <si>
-    <t>home_delivery_helper</t>
-  </si>
-  <si>
-    <t>traditional_birth_attendant</t>
-  </si>
-  <si>
-    <t>Traditional birth attendant</t>
-  </si>
-  <si>
-    <t>Kujifungua kwa mkunga wa kienyeji/jadi.</t>
-  </si>
-  <si>
-    <t>family_member</t>
+    <t>infection</t>
+  </si>
+  <si>
+    <t>Infection (high fever right after delivery)</t>
+  </si>
+  <si>
+    <t>Je ulipata Maambukizi ( Homa kali baada tu ya kujifungua) ?</t>
   </si>
   <si>
     <t>selected(${delivery_facility},"other")</t>
   </si>
   <si>
-    <t>Family member</t>
-  </si>
-  <si>
-    <t>Kwa msaada wa wanafamilia</t>
-  </si>
-  <si>
-    <t>neighbor_friend</t>
-  </si>
-  <si>
-    <t>Neighbor / friend</t>
-  </si>
-  <si>
-    <t>Jirani/Rafika</t>
-  </si>
-  <si>
-    <t>no_one</t>
-  </si>
-  <si>
-    <t>No one</t>
-  </si>
-  <si>
-    <t>Hapana kati ya hizo</t>
-  </si>
-  <si>
-    <t>immediate_cry</t>
-  </si>
-  <si>
-    <t>Yes: Cried immediately, no problem breathing.</t>
+    <t>prolonged_labor</t>
+  </si>
+  <si>
+    <t>Prolonged labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ulipata uchungu wa muda mrefu sana ? </t>
+  </si>
+  <si>
+    <t>large_perineal_tear</t>
+  </si>
+  <si>
+    <t>Large perineal tear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je mtoto alichana msamba/njia ya uzazi kwa kiasi kikubwa ? </t>
+  </si>
+  <si>
+    <t>retained_placenta</t>
+  </si>
+  <si>
+    <t>Retained placenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je zalio/kondo la nyuma lilichelewa ? </t>
+  </si>
+  <si>
+    <t>dont_know</t>
+  </si>
+  <si>
+    <t>Does not know</t>
+  </si>
+  <si>
+    <t>Sijui</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>None of the above</t>
+  </si>
+  <si>
+    <t>Hakuna iliotokezea</t>
+  </si>
+  <si>
+    <t>how_handled</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>Good/great</t>
+  </si>
+  <si>
+    <t>Vizuri</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somehow good / ok </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afadhali </t>
+  </si>
+  <si>
+    <t>bad</t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>Vibaya</t>
   </si>
   <si>
     <t>delivery_information</t>
   </si>
   <si>
-    <t>Ndio: Alilia punde tu baada ya kuzaliwa, na hakuwa na tatatizo la kupumua.</t>
+    <t>why_handled_bad</t>
   </si>
   <si>
     <t>Delivery Information</t>
   </si>
   <si>
+    <t>shouted</t>
+  </si>
+  <si>
     <t>Taarifa za kujifungua.</t>
   </si>
   <si>
-    <t>No: Had difficulty breathing at birth or require resuscitation.</t>
-  </si>
-  <si>
-    <t>Hapana: Alipata tatizo la upumuwaji alipozaliwa au alihitaji msaada wa kidaktari ili aweze kupumua</t>
+    <t>Shouted at</t>
+  </si>
+  <si>
+    <t>Kukaripiwa</t>
   </si>
   <si>
     <t>select_one method_facility_delivery</t>
   </si>
   <si>
-    <t>major_complications</t>
-  </si>
-  <si>
     <t>facility_delivery_method</t>
   </si>
   <si>
-    <t>antepartum_hemorrhage</t>
-  </si>
-  <si>
     <t>What was the method of delivery?</t>
   </si>
   <si>
-    <t>Antepartum hemorrhage</t>
-  </si>
-  <si>
     <t>Ulijifungua kwa njia gani?</t>
   </si>
   <si>
-    <t xml:space="preserve">Je ulitokwa na damu nyingi kabla ya kujifungua? </t>
-  </si>
-  <si>
-    <t>intrapartum_hemorrhage</t>
-  </si>
-  <si>
-    <t>Intrapartum hemorrhage</t>
-  </si>
-  <si>
     <t>select_one home_delivery_helper</t>
   </si>
   <si>
-    <t xml:space="preserve">Je ulitokwa na damu nyingi wakati wa kujifungua? </t>
-  </si>
-  <si>
     <t>Who was the main person who helped you deliver the baby?</t>
   </si>
   <si>
     <t>Nani muhusika mkuu aliekusaidia wakati ukimzaa mtoto wako?</t>
   </si>
   <si>
-    <t>postpartum_hemorrhage</t>
-  </si>
-  <si>
-    <t>Postpartum hemorrhage</t>
+    <t>hit</t>
   </si>
   <si>
     <t>not(selected(${delivery_location},"facility"))</t>
   </si>
   <si>
-    <t>Je ulitokwa na damu nyingi baada ya kujifungua?</t>
+    <t>Slapped or hit</t>
+  </si>
+  <si>
+    <t>Kupigwa</t>
   </si>
   <si>
     <t>select_one yes_no</t>
   </si>
   <si>
-    <t>preeclampsia_eclampsia</t>
-  </si>
-  <si>
     <t>got_facility_pnc</t>
   </si>
   <si>
-    <t>Preeclampsia, eclampsia, or hypertension related</t>
+    <t>ignored</t>
   </si>
   <si>
     <t xml:space="preserve">Since the birth of the child, have you and your baby gone to a healthcare facility for postnatal care? </t>
   </si>
   <si>
-    <t>Kifafa cha mimba kabla ya kujifungua, Kifafa cha mimba or pressuere ya kupanda.</t>
+    <t>Ignored</t>
   </si>
   <si>
     <t>Tokea umzae mtoto wako, wewe na mtoto wako mumesha wahi kwenda kituo cha afya kupata huduma za baada ya kujifungua?</t>
   </si>
   <si>
-    <t>infection</t>
-  </si>
-  <si>
-    <t>Infection (high fever right after delivery)</t>
-  </si>
-  <si>
-    <t>Je ulipata Maambukizi ( Homa kali baada tu ya kujifungua) ?</t>
+    <t>Kudharauliwa</t>
+  </si>
+  <si>
+    <t>unfriendly</t>
+  </si>
+  <si>
+    <t>People were not friendly</t>
   </si>
   <si>
     <t>got_facility_pnc_note</t>
   </si>
   <si>
+    <t xml:space="preserve">Sio wakarimu </t>
+  </si>
+  <si>
     <t>Great! Congratulations on everything.</t>
   </si>
   <si>
@@ -1083,271 +1231,229 @@
     <t>selected(${got_facility_pnc},"yes")</t>
   </si>
   <si>
+    <t xml:space="preserve">Nyengine </t>
+  </si>
+  <si>
     <t>didnt_get_facility_pnc_note</t>
   </si>
   <si>
+    <t>how_much_paid</t>
+  </si>
+  <si>
     <t>Congratulations on the birth of your baby. Now, it is very important for you to take them to a healthcare facility in order to check you and your baby’s health and for them to get the vaccines and other important services they need. You should go to the facility as soon as possible for this care – even today.</t>
   </si>
   <si>
+    <t>&lt;1,000</t>
+  </si>
+  <si>
+    <t>Less than one thousand</t>
+  </si>
+  <si>
     <t>Hongera sana kwa kupata mtoto, Ila kwa sasa, ni muhimu sana kwenda nae (nao) katika kituo cha afya ili wewe na yeye (wao) mukachekiwe afya zenu, na mtoto/watoto kupata chanjo na huduma nyengine muhimu ambazo wanazihitaji. Na ni vizuri kwenda katika kituo cha afya haraka iwezekezekanavyo - hata leo hii.</t>
   </si>
   <si>
+    <t>Chini ya Shilingi elfu moja</t>
+  </si>
+  <si>
     <t>selected(${got_facility_pnc},"no")</t>
   </si>
   <si>
-    <t>prolonged_labor</t>
-  </si>
-  <si>
-    <t>Prolonged labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je ulipata uchungu wa muda mrefu sana ? </t>
+    <t>1,000 - 10,000</t>
+  </si>
+  <si>
+    <t>Between one thousand and ten thousand</t>
   </si>
   <si>
     <t>refer_flag_no_facility_pnc</t>
   </si>
   <si>
-    <t>large_perineal_tear</t>
+    <t xml:space="preserve">Kati ya shilingi elfu na shilingi elfu kumi </t>
+  </si>
+  <si>
+    <t>10,000 - 20,000</t>
   </si>
   <si>
     <t>if(selected(${got_facility_pnc},"no"),1,0)</t>
   </si>
   <si>
-    <t>Large perineal tear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je mtoto alichana msamba/njia ya uzazi kwa kiasi kikubwa ? </t>
+    <t>Between ten thousand and twenty thousand</t>
+  </si>
+  <si>
+    <t>Kati ya shilingi elfu kumi  na shilingi elfu ishirini</t>
   </si>
   <si>
     <t>born_early</t>
   </si>
   <si>
-    <t>retained_placenta</t>
-  </si>
-  <si>
     <t>Was the baby born preterm or too early?</t>
   </si>
   <si>
-    <t>Retained placenta</t>
+    <t>20,000 - 50,000</t>
+  </si>
+  <si>
+    <t>Between twenty thousand and fifty thousand</t>
   </si>
   <si>
     <t>Je mtoto alifika muda wake wa kuzaliwa?</t>
   </si>
   <si>
-    <t xml:space="preserve">Je zalio/kondo la nyuma lilichelewa ? </t>
+    <t>Kati ya shilingi elfu ishirini na shilingi elfu hamsini</t>
+  </si>
+  <si>
+    <t>&gt;50,000</t>
+  </si>
+  <si>
+    <t>Over fifty thousand</t>
+  </si>
+  <si>
+    <t>Zaidi ya shilingi elfu hamsini</t>
   </si>
   <si>
     <t>select_one immediate_cry</t>
   </si>
   <si>
+    <t>what_supplies_purchased</t>
+  </si>
+  <si>
+    <t>gloves</t>
+  </si>
+  <si>
     <t>Did the baby cry immediately after birth?</t>
   </si>
   <si>
-    <t>dont_know</t>
+    <t>Gloves</t>
   </si>
   <si>
     <t>Je mtoto alilia punde tu baada ya kuzaliwa?</t>
   </si>
   <si>
-    <t>Does not know</t>
-  </si>
-  <si>
-    <t>Sijui</t>
-  </si>
-  <si>
-    <t>none</t>
+    <t>plastic_sheet</t>
+  </si>
+  <si>
+    <t>Plastic sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mpira </t>
   </si>
   <si>
     <t>admitted_after_birth</t>
   </si>
   <si>
-    <t>None of the above</t>
-  </si>
-  <si>
     <t>Was baby admitted to neonatal unit/special care area/hospital within the first 24 hours after birth?</t>
   </si>
   <si>
-    <t>Hakuna iliotokezea</t>
+    <t>medicine</t>
   </si>
   <si>
     <t>Je, mtoto aliwahi kulazwa hospital katika wodi maalum ya watoto wachanga ndani ya masaa 24 ya mwanzo baada ya kuzaliwa?</t>
   </si>
   <si>
-    <t>how_handled</t>
-  </si>
-  <si>
-    <t>good</t>
-  </si>
-  <si>
-    <t>Good/great</t>
+    <t>Medicine</t>
+  </si>
+  <si>
+    <t>Dawa</t>
+  </si>
+  <si>
+    <t>cleaning_supplies</t>
+  </si>
+  <si>
+    <t>Cleaning supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vifaa vya kusafishia </t>
   </si>
   <si>
     <t>select_multiple major_complications</t>
   </si>
   <si>
-    <t>Vizuri</t>
+    <t>needles</t>
   </si>
   <si>
     <t xml:space="preserve">Did the woman experience any of these major medical complications during this delivery? </t>
   </si>
   <si>
+    <t>Needles/syringe</t>
+  </si>
+  <si>
+    <t>Sindano</t>
+  </si>
+  <si>
     <t>Je mama alipata matatizo makubwa ya kiafya muda mfupi baada ya kujifungua?</t>
   </si>
   <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somehow good / ok </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afadhali </t>
+    <t>iv_infusion</t>
   </si>
   <si>
     <t>(selected(.,"none") and count-selected(.)=1) or (not(selected(.,"none")) and count-selected(.)&gt;=1)</t>
   </si>
   <si>
+    <t>IV Infusion</t>
+  </si>
+  <si>
+    <t>Dripu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cannot select "None of the above" with other options </t>
   </si>
   <si>
-    <t>bad</t>
-  </si>
-  <si>
-    <t>Bad</t>
-  </si>
-  <si>
-    <t>Vibaya</t>
-  </si>
-  <si>
-    <t>why_handled_bad</t>
-  </si>
-  <si>
-    <t>shouted</t>
-  </si>
-  <si>
-    <t>Shouted at</t>
-  </si>
-  <si>
-    <t>Kukaripiwa</t>
-  </si>
-  <si>
-    <t>hit</t>
-  </si>
-  <si>
-    <t>Slapped or hit</t>
+    <t>did_deliver</t>
+  </si>
+  <si>
+    <t>Mother has delivered</t>
   </si>
   <si>
     <t>Huwezi kuchaguwa "Hakuna moja wapo" na chaguo jengine</t>
   </si>
   <si>
-    <t>Kupigwa</t>
-  </si>
-  <si>
-    <t>ignored</t>
-  </si>
-  <si>
-    <t>Ignored</t>
-  </si>
-  <si>
-    <t>Kudharauliwa</t>
-  </si>
-  <si>
-    <t>unfriendly</t>
-  </si>
-  <si>
     <t>number_deliveries</t>
   </si>
   <si>
-    <t>People were not friendly</t>
-  </si>
-  <si>
     <t>Number of Deliveries</t>
   </si>
   <si>
-    <t xml:space="preserve">Sio wakarimu </t>
-  </si>
-  <si>
     <t>Idadi ya watoto alioifungua /aliozaa.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nyengine </t>
-  </si>
-  <si>
     <t>select_one num_deliveries</t>
   </si>
   <si>
     <t>check_multiple_deliveries</t>
   </si>
   <si>
-    <t>how_much_paid</t>
-  </si>
-  <si>
     <t>Did you deliver one baby or more than one baby</t>
   </si>
   <si>
-    <t>&lt;1,000</t>
-  </si>
-  <si>
     <t xml:space="preserve">Je umejifungua mtoto mmoja au zaidi ya mtoto mmoja? </t>
   </si>
   <si>
-    <t>Less than one thousand</t>
-  </si>
-  <si>
-    <t>Chini ya Shilingi elfu moja</t>
-  </si>
-  <si>
     <t>integer</t>
   </si>
   <si>
-    <t>1,000 - 10,000</t>
-  </si>
-  <si>
     <t>num_babies_delivered</t>
   </si>
   <si>
-    <t>Between one thousand and ten thousand</t>
-  </si>
-  <si>
     <t>How many babies did you deliver?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kati ya shilingi elfu na shilingi elfu kumi </t>
-  </si>
-  <si>
     <t xml:space="preserve">Je umejifungua watoto wangapi? </t>
   </si>
   <si>
     <t>selected(${check_multiple_deliveries},"more")</t>
   </si>
   <si>
-    <t>10,000 - 20,000</t>
-  </si>
-  <si>
     <t>2 &lt;= . and . &lt;= 4</t>
   </si>
   <si>
-    <t>Between ten thousand and twenty thousand</t>
-  </si>
-  <si>
     <t>Delivery of between 2 and 4 babies is supported</t>
   </si>
   <si>
-    <t>Kati ya shilingi elfu kumi  na shilingi elfu ishirini</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tafadhali ingiza idadi kati ya 2 na 4. </t>
   </si>
   <si>
-    <t>20,000 - 50,000</t>
-  </si>
-  <si>
-    <t>Between twenty thousand and fifty thousand</t>
-  </si>
-  <si>
     <t>live_birth</t>
   </si>
   <si>
-    <t>Kati ya shilingi elfu ishirini na shilingi elfu hamsini</t>
+    <t xml:space="preserve">Mama amejifungua </t>
   </si>
   <si>
     <t>Is the baby alive?</t>
@@ -1356,34 +1462,31 @@
     <t xml:space="preserve">Mtoto yuko hai? </t>
   </si>
   <si>
-    <t>&gt;50,000</t>
-  </si>
-  <si>
     <t>selected(${check_multiple_deliveries},"one")</t>
   </si>
   <si>
-    <t>Over fifty thousand</t>
-  </si>
-  <si>
-    <t>Zaidi ya shilingi elfu hamsini</t>
+    <t>Mother suffered a miscarriage or stillbirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mimba imeharibika au mtoto kafa tumboni </t>
   </si>
   <si>
     <t>num_live_births</t>
   </si>
   <si>
-    <t>what_supplies_purchased</t>
+    <t>temp_perm</t>
   </si>
   <si>
     <t>How many of the babies are alive?</t>
   </si>
   <si>
-    <t>gloves</t>
+    <t>permanent</t>
   </si>
   <si>
     <t xml:space="preserve">Watoto wangapi wako hai? </t>
   </si>
   <si>
-    <t>Gloves</t>
+    <t>Permanent household member - not planning to move elsewhere</t>
   </si>
   <si>
     <t>0 &lt;= . and . &lt;= ${num_babies_delivered}</t>
@@ -1392,28 +1495,10 @@
     <t>Enter a number between 0 and the total number of babies delivered</t>
   </si>
   <si>
-    <t>plastic_sheet</t>
-  </si>
-  <si>
     <t>Ingiza nambari baina ya 0 na jumla ya watoto waliozaliwa.</t>
   </si>
   <si>
-    <t>Plastic sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mpira </t>
-  </si>
-  <si>
-    <t>medicine</t>
-  </si>
-  <si>
-    <t>Medicine</t>
-  </si>
-  <si>
     <t>child_death_count</t>
-  </si>
-  <si>
-    <t>Dawa</t>
   </si>
   <si>
     <t>if(selected(${check_multiple_deliveries},"one") and selected(${live_birth},"yes"),
@@ -1423,39 +1508,21 @@
          ${num_babies_delivered} - ${num_live_births}))</t>
   </si>
   <si>
-    <t>cleaning_supplies</t>
-  </si>
-  <si>
-    <t>Cleaning supplies</t>
-  </si>
-  <si>
     <t>child_death_note</t>
   </si>
   <si>
-    <t xml:space="preserve">Vifaa vya kusafishia </t>
-  </si>
-  <si>
-    <t>needles</t>
-  </si>
-  <si>
     <t>I'm very sorry for your loss</t>
   </si>
   <si>
-    <t>Needles/syringe</t>
-  </si>
-  <si>
     <t>Pole sana kwa kupoteza mtoto wako.</t>
   </si>
   <si>
-    <t>Sindano</t>
+    <t>Mkaazi wa kudumu - Hatohamia sehemu nyengine</t>
   </si>
   <si>
     <t>${child_death_count} &gt; 0</t>
   </si>
   <si>
-    <t>iv_infusion</t>
-  </si>
-  <si>
     <t>multiple_child_death_note</t>
   </si>
   <si>
@@ -1468,12 +1535,6 @@
     <t>${child_death_count} &gt; 1</t>
   </si>
   <si>
-    <t>IV Infusion</t>
-  </si>
-  <si>
-    <t>Dripu</t>
-  </si>
-  <si>
     <t>begin repeat</t>
   </si>
   <si>
@@ -1486,18 +1547,21 @@
     <t>Taarifa za kifo cha mtoto</t>
   </si>
   <si>
-    <t>did_deliver</t>
-  </si>
-  <si>
-    <t>Mother has delivered</t>
-  </si>
-  <si>
     <t>selected(${pregnancy_outcome},"did_deliver") and ${child_death_count} &gt; 0</t>
   </si>
   <si>
+    <t>temporary</t>
+  </si>
+  <si>
+    <t>Temporary household member - planning to move elsewhere soon</t>
+  </si>
+  <si>
     <t>${child_death_count}</t>
   </si>
   <si>
+    <t>Mkaazi wa muda - Atahamia sehemu nyengine</t>
+  </si>
+  <si>
     <t>child_date_of_death</t>
   </si>
   <si>
@@ -1519,37 +1583,19 @@
     <t>end repeat</t>
   </si>
   <si>
-    <t xml:space="preserve">Mama amejifungua </t>
-  </si>
-  <si>
     <t>child_repeat_count</t>
   </si>
   <si>
-    <t>Mother suffered a miscarriage or stillbirth</t>
-  </si>
-  <si>
     <t>if(selected(${check_multiple_deliveries},"one") and selected(${live_birth},"yes"),1,if(selected(${check_multiple_deliveries},"one") and selected(${live_birth},"no"),0,${num_live_births}))</t>
   </si>
   <si>
-    <t xml:space="preserve">Mimba imeharibika au mtoto kafa tumboni </t>
-  </si>
-  <si>
     <t>intro_data_capture</t>
   </si>
   <si>
-    <t>temp_perm</t>
-  </si>
-  <si>
     <t>Capture Child Data</t>
   </si>
   <si>
-    <t>permanent</t>
-  </si>
-  <si>
     <t>Taarifa za mtoto.</t>
-  </si>
-  <si>
-    <t>Permanent household member - not planning to move elsewhere</t>
   </si>
   <si>
     <t>selected(${pregnancy_outcome},"did_deliver") and ${child_repeat_count} &gt; 0</t>
@@ -1577,24 +1623,12 @@
     <t>child</t>
   </si>
   <si>
-    <t>Mkaazi wa kudumu - Hatohamia sehemu nyengine</t>
-  </si>
-  <si>
     <t>${child_repeat_count}</t>
   </si>
   <si>
     <t>true</t>
   </si>
   <si>
-    <t>temporary</t>
-  </si>
-  <si>
-    <t>Temporary household member - planning to move elsewhere soon</t>
-  </si>
-  <si>
-    <t>Mkaazi wa muda - Atahamia sehemu nyengine</t>
-  </si>
-  <si>
     <t>first_name</t>
   </si>
   <si>
@@ -1649,12 +1683,6 @@
     <t>${date_of_delivery}</t>
   </si>
   <si>
-    <t>child_doc</t>
-  </si>
-  <si>
-    <t>${child}</t>
-  </si>
-  <si>
     <t>created_by_doc</t>
   </si>
   <si>
@@ -1689,6 +1717,27 @@
   </si>
   <si>
     <t>person</t>
+  </si>
+  <si>
+    <t>meta</t>
+  </si>
+  <si>
+    <t>created_by</t>
+  </si>
+  <si>
+    <t>../../../name</t>
+  </si>
+  <si>
+    <t>created_by_person_uuid</t>
+  </si>
+  <si>
+    <t>../../../contact_id</t>
+  </si>
+  <si>
+    <t>created_by_place_uuid</t>
+  </si>
+  <si>
+    <t>../../../facility_id</t>
   </si>
   <si>
     <t>quality_of_care_survey</t>
@@ -1788,7 +1837,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1814,6 +1863,10 @@
     <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <color rgb="FF1D1C1D"/>
+      <name val="Slack-Lato"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -1855,7 +1908,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1874,17 +1927,20 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -1914,12 +1970,21 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1928,13 +1993,10 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1988,47 +2050,48 @@
     <col customWidth="1" min="4" max="4" width="44.0"/>
     <col customWidth="1" min="6" max="6" width="29.0"/>
     <col customWidth="1" min="11" max="11" width="21.0"/>
+    <col customWidth="1" min="20" max="20" width="23.86"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>15</v>
@@ -2043,376 +2106,376 @@
         <v>18</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="S1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>55</v>
+        <v>40</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>64</v>
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>80</v>
+        <v>31</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C20" s="1"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C24" s="1"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="8"/>
-      <c r="Z25" s="8"/>
+      <c r="A25" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="8"/>
-      <c r="Z26" s="8"/>
+      <c r="A26" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
-      <c r="W27" s="8"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="8"/>
-      <c r="Z27" s="8"/>
+      <c r="A27" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -2423,16 +2486,16 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-      <c r="L28" s="11" t="s">
-        <v>137</v>
+      <c r="L28" s="12" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -2443,16 +2506,16 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="11" t="s">
-        <v>142</v>
+      <c r="L29" s="12" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -2464,15 +2527,15 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -2484,15 +2547,15 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -2504,15 +2567,15 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -2523,16 +2586,16 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="12" t="s">
-        <v>154</v>
+      <c r="L33" s="13" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>158</v>
+        <v>75</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>142</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -2544,15 +2607,15 @@
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="3" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>164</v>
+        <v>75</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -2564,15 +2627,15 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="3" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>167</v>
+        <v>75</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -2584,15 +2647,15 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="3" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>173</v>
+      <c r="A37" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>150</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -2603,16 +2666,16 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="15" t="s">
-        <v>175</v>
+      <c r="L37" s="16" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>176</v>
+      <c r="A38" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>155</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -2623,16 +2686,16 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="15" t="s">
-        <v>178</v>
+      <c r="L38" s="16" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>179</v>
+      <c r="A39" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>159</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -2643,16 +2706,16 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="15" t="s">
-        <v>181</v>
+      <c r="L39" s="16" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>182</v>
+      <c r="A40" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>162</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -2663,28 +2726,28 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="15" t="s">
-        <v>184</v>
+      <c r="L40" s="16" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C41" s="16"/>
+        <v>165</v>
+      </c>
+      <c r="C41" s="17"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="16"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="17" t="s">
-        <v>189</v>
+      <c r="L41" s="18" t="s">
+        <v>168</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
@@ -2703,21 +2766,21 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C42" s="16"/>
+        <v>172</v>
+      </c>
+      <c r="C42" s="17"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="16"/>
+      <c r="G42" s="17"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="18">
+      <c r="L42" s="19">
         <v>7.0</v>
       </c>
       <c r="M42" s="1"/>
@@ -2737,21 +2800,21 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C43" s="16"/>
+        <v>178</v>
+      </c>
+      <c r="C43" s="17"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="16"/>
+      <c r="G43" s="17"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="18">
+      <c r="L43" s="19">
         <v>30.0</v>
       </c>
       <c r="M43" s="1"/>
@@ -2770,367 +2833,360 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="1" t="s">
+      <c r="A44" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="20"/>
+    </row>
+    <row r="45" ht="18.75" customHeight="1">
+      <c r="A45" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C45" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="D44" s="19" t="s">
+      <c r="D45" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>210</v>
-      </c>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="20"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="20"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>216</v>
-      </c>
+      <c r="A46" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="20"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="20"/>
+      <c r="R46" s="20"/>
+      <c r="S46" s="20"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>206</v>
+        <v>29</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D47" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>200</v>
+      <c r="C48" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>205</v>
+      <c r="A49" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>24</v>
+      <c r="A50" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>234</v>
+        <v>52</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="K51" s="22" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>206</v>
+        <v>29</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2" t="s">
-        <v>249</v>
+        <v>240</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>253</v>
+        <v>244</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>246</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>249</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>124</v>
+        <v>249</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K54" s="26" t="s">
         <v>256</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="L54" s="2" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>44</v>
+        <v>249</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F56" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="Q57" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="L57" s="2" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>266</v>
+        <v>52</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="G58" s="2"/>
-      <c r="Q58" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="C58" s="2"/>
     </row>
     <row r="59">
-      <c r="A59" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="B59" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="C59" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>24</v>
+      <c r="A59" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="G59" s="16"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="16"/>
-      <c r="R59" s="1"/>
-      <c r="S59" s="1"/>
-      <c r="T59" s="1"/>
-      <c r="U59" s="1"/>
-      <c r="V59" s="1"/>
-      <c r="W59" s="1"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
+        <v>253</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>280</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="M60" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="Q60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G61" s="2"/>
-      <c r="M61" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="Q61" s="2"/>
     </row>
     <row r="62">
-      <c r="A62" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="C62" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="E62" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F62" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="G62" s="16"/>
+      <c r="A62" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C62" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="G62" s="17"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -3140,7 +3196,7 @@
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
-      <c r="Q62" s="16"/>
+      <c r="Q62" s="17"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
@@ -3153,1040 +3209,1284 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>70</v>
+        <v>312</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="F63" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>318</v>
+      </c>
       <c r="G63" s="2"/>
+      <c r="M63" s="2" t="s">
+        <v>320</v>
+      </c>
       <c r="Q63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>44</v>
+        <v>322</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>312</v>
+        <v>131</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F64" s="20" t="s">
-        <v>239</v>
+        <v>326</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>328</v>
       </c>
       <c r="G64" s="2"/>
+      <c r="M64" s="2" t="s">
+        <v>330</v>
+      </c>
       <c r="Q64" s="2"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="G65" s="2"/>
-      <c r="Q65" s="2"/>
+      <c r="A65" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C65" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="G65" s="17"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="17"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>328</v>
+        <v>52</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>334</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="Q66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>336</v>
+        <v>29</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>334</v>
+        <v>366</v>
+      </c>
+      <c r="F67" s="24" t="s">
+        <v>253</v>
       </c>
       <c r="G67" s="2"/>
       <c r="Q67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>206</v>
+        <v>369</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>348</v>
+        <v>372</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>349</v>
+        <v>293</v>
       </c>
       <c r="G68" s="2"/>
       <c r="Q68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>206</v>
+        <v>373</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>350</v>
+        <v>279</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>352</v>
+        <v>375</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="G69" s="2"/>
       <c r="Q69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>124</v>
+        <v>380</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="F70" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>377</v>
+      </c>
       <c r="G70" s="2"/>
-      <c r="L70" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="Q70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>336</v>
+        <v>198</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F71" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>393</v>
+      </c>
       <c r="G71" s="2"/>
       <c r="Q71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>368</v>
+        <v>198</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>310</v>
+        <v>395</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>402</v>
+      </c>
       <c r="G72" s="2"/>
       <c r="Q72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>336</v>
+        <v>75</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
+      <c r="L73" s="2" t="s">
+        <v>408</v>
+      </c>
       <c r="Q73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>319</v>
+        <v>411</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>386</v>
+        <v>415</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-      <c r="I74" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="J74" s="25" t="s">
-        <v>391</v>
-      </c>
-      <c r="K74" s="25" t="s">
-        <v>401</v>
-      </c>
       <c r="Q74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C75" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="Q75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>44</v>
+        <v>380</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="F76" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>205</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="Q76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>414</v>
+        <v>309</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="I77" s="24" t="s">
+        <v>445</v>
+      </c>
+      <c r="J77" s="28" t="s">
+        <v>448</v>
+      </c>
+      <c r="K77" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>421</v>
+        <v>52</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>434</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="Q78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>336</v>
+        <v>29</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>442</v>
+        <v>454</v>
+      </c>
+      <c r="F79" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>454</v>
+        <v>41</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>70</v>
+        <v>459</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>407</v>
+        <v>460</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>124</v>
+        <v>380</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="L82" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>206</v>
+        <v>459</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>469</v>
+        <v>478</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="G83" s="2"/>
-      <c r="L83" s="2"/>
-      <c r="Q83" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>482</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>206</v>
+        <v>52</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="G84" s="2"/>
-      <c r="L84" s="2"/>
-      <c r="Q84" s="2"/>
+        <v>452</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>479</v>
+        <v>75</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="L85" s="2"/>
-      <c r="Q85" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="D86" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="J86" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>492</v>
-      </c>
+      <c r="G86" s="2"/>
       <c r="L86" s="2"/>
+      <c r="Q86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>480</v>
-      </c>
+      <c r="G87" s="2"/>
       <c r="L87" s="2"/>
+      <c r="Q87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>124</v>
+        <v>494</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="L88" s="2" t="s">
+      <c r="C88" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>497</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="L88" s="2"/>
+      <c r="Q88" s="2" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>44</v>
+        <v>249</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F89" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="G89" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q89" s="2"/>
+      <c r="E89" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="L89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>206</v>
+        <v>509</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C90" s="25" t="s">
-        <v>507</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="Q90" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="L90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>206</v>
+        <v>75</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C91" s="25" t="s">
         <v>510</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="L91" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>479</v>
+        <v>29</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>512</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>46</v>
+        <v>513</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>46</v>
+        <v>514</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>515</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q92" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="T92" s="29" t="s">
-        <v>515</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Q92" s="2"/>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="B93" s="8" t="s">
+      <c r="A93" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C93" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q93" s="2"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C94" s="28" t="s">
         <v>520</v>
       </c>
-      <c r="D93" s="14" t="s">
+      <c r="D94" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="E93" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="B94" s="30" t="s">
+      <c r="F94" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q94" s="2"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C95" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q95" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="D94" s="14" t="s">
+      <c r="T95" s="32" t="s">
         <v>524</v>
       </c>
-      <c r="E94" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="30" t="s">
-        <v>270</v>
-      </c>
-      <c r="B95" s="30" t="s">
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B96" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="C95" s="14" t="s">
+      <c r="C96" s="15" t="s">
         <v>526</v>
       </c>
-      <c r="D95" s="14" t="s">
+      <c r="D96" s="15" t="s">
         <v>527</v>
       </c>
-      <c r="E95" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="B96" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="24" t="s">
+      <c r="E96" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="B97" s="33" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="s">
+      <c r="C97" s="15" t="s">
         <v>529</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="D97" s="15" t="s">
         <v>530</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="E97" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="B98" s="33" t="s">
         <v>531</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="23" t="s">
+      <c r="C98" s="15" t="s">
         <v>532</v>
       </c>
-      <c r="B98" s="23" t="s">
+      <c r="D98" s="15" t="s">
         <v>533</v>
       </c>
-      <c r="C98" s="24" t="s">
+      <c r="E98" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B99" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
+      <c r="I99" s="9"/>
+      <c r="J99" s="9"/>
+      <c r="K99" s="9"/>
+      <c r="L99" s="10" t="s">
         <v>534</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E98" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="L98" s="2"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>124</v>
+        <v>535</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="L100" s="2" t="s">
+      <c r="E100" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="27" t="s">
         <v>538</v>
       </c>
-      <c r="U100" s="2" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="27" t="s">
         <v>539</v>
       </c>
-      <c r="L101" s="2" t="s">
+      <c r="C101" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="U101" s="2" t="s">
+      <c r="D101" s="2" t="s">
         <v>541</v>
       </c>
+      <c r="E101" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>46</v>
+        <v>65</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
+      </c>
+      <c r="U103" s="2" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>97</v>
+        <v>61</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="L111" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="P111" s="2" t="s">
-        <v>550</v>
+        <v>66</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>493</v>
+        <v>52</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>512</v>
+        <v>66</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>499</v>
+        <v>0</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="D114" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="G114" s="2"/>
-      <c r="Q114" s="2"/>
+      <c r="A114" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B114" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D114" s="9"/>
+      <c r="E114" s="9"/>
+      <c r="F114" s="9"/>
+      <c r="G114" s="9"/>
+      <c r="H114" s="9"/>
+      <c r="I114" s="9"/>
+      <c r="J114" s="9"/>
+      <c r="K114" s="9"/>
+      <c r="L114" s="9"/>
+      <c r="M114" s="9"/>
+      <c r="N114" s="9"/>
+      <c r="O114" s="9"/>
+      <c r="P114" s="9"/>
+      <c r="Q114" s="9"/>
+      <c r="R114" s="9"/>
+      <c r="S114" s="9"/>
+      <c r="T114" s="9"/>
+      <c r="U114" s="9"/>
+      <c r="V114" s="9"/>
+      <c r="W114" s="9"/>
+      <c r="X114" s="9"/>
+      <c r="Y114" s="9"/>
+      <c r="Z114" s="9"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B115" s="2" t="s">
+      <c r="A115" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B115" s="33" t="s">
+        <v>556</v>
+      </c>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="9"/>
+      <c r="F115" s="9"/>
+      <c r="G115" s="9"/>
+      <c r="H115" s="9"/>
+      <c r="I115" s="9"/>
+      <c r="J115" s="9"/>
+      <c r="K115" s="9"/>
+      <c r="L115" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="M115" s="9"/>
+      <c r="N115" s="9"/>
+      <c r="O115" s="9"/>
+      <c r="P115" s="9"/>
+      <c r="Q115" s="9"/>
+      <c r="R115" s="9"/>
+      <c r="S115" s="9"/>
+      <c r="T115" s="9"/>
+      <c r="U115" s="9"/>
+      <c r="V115" s="9"/>
+      <c r="W115" s="9"/>
+      <c r="X115" s="9"/>
+      <c r="Y115" s="9"/>
+      <c r="Z115" s="9"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B116" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="9"/>
+      <c r="F116" s="9"/>
+      <c r="G116" s="9"/>
+      <c r="H116" s="9"/>
+      <c r="I116" s="9"/>
+      <c r="J116" s="9"/>
+      <c r="K116" s="9"/>
+      <c r="L116" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="M116" s="9"/>
+      <c r="N116" s="9"/>
+      <c r="O116" s="9"/>
+      <c r="P116" s="9"/>
+      <c r="Q116" s="9"/>
+      <c r="R116" s="9"/>
+      <c r="S116" s="9"/>
+      <c r="T116" s="9"/>
+      <c r="U116" s="9"/>
+      <c r="V116" s="9"/>
+      <c r="W116" s="9"/>
+      <c r="X116" s="9"/>
+      <c r="Y116" s="9"/>
+      <c r="Z116" s="9"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B117" s="33" t="s">
+        <v>560</v>
+      </c>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="9"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="9"/>
+      <c r="H117" s="9"/>
+      <c r="I117" s="9"/>
+      <c r="J117" s="9"/>
+      <c r="K117" s="9"/>
+      <c r="L117" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="M117" s="9"/>
+      <c r="N117" s="9"/>
+      <c r="O117" s="9"/>
+      <c r="P117" s="9"/>
+      <c r="Q117" s="9"/>
+      <c r="R117" s="9"/>
+      <c r="S117" s="9"/>
+      <c r="T117" s="9"/>
+      <c r="U117" s="9"/>
+      <c r="V117" s="9"/>
+      <c r="W117" s="9"/>
+      <c r="X117" s="9"/>
+      <c r="Y117" s="9"/>
+      <c r="Z117" s="9"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B118" s="33" t="s">
         <v>555</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D115" s="32" t="s">
-        <v>557</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="Q115" s="2"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="G116" s="2"/>
-      <c r="Q116" s="2"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="G117" s="2"/>
-      <c r="Q117" s="2"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="G118" s="2"/>
-      <c r="Q118" s="2"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
+      <c r="E118" s="9"/>
+      <c r="F118" s="9"/>
+      <c r="G118" s="9"/>
+      <c r="H118" s="9"/>
+      <c r="I118" s="9"/>
+      <c r="J118" s="9"/>
+      <c r="K118" s="9"/>
+      <c r="L118" s="9"/>
+      <c r="M118" s="9"/>
+      <c r="N118" s="9"/>
+      <c r="O118" s="9"/>
+      <c r="P118" s="9"/>
+      <c r="Q118" s="9"/>
+      <c r="R118" s="9"/>
+      <c r="S118" s="9"/>
+      <c r="T118" s="9"/>
+      <c r="U118" s="9"/>
+      <c r="V118" s="9"/>
+      <c r="W118" s="9"/>
+      <c r="X118" s="9"/>
+      <c r="Y118" s="9"/>
+      <c r="Z118" s="9"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>336</v>
+        <v>509</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="G119" s="2"/>
-      <c r="Q119" s="2"/>
+        <v>522</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>574</v>
+        <v>52</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="G120" s="2"/>
-      <c r="Q120" s="2"/>
+        <v>512</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>336</v>
+        <v>29</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>24</v>
+        <v>563</v>
+      </c>
+      <c r="D121" s="34" t="s">
+        <v>564</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="G121" s="2"/>
       <c r="Q121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>70</v>
+        <v>380</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D122" s="35" t="s">
+        <v>568</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="Q122" s="2"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="G123" s="2"/>
+      <c r="Q123" s="2"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="G124" s="2"/>
+      <c r="Q124" s="2"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="G125" s="2"/>
+      <c r="Q125" s="2"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="G126" s="2"/>
+      <c r="Q126" s="2"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="G127" s="2"/>
+      <c r="Q127" s="2"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="G128" s="2"/>
+      <c r="Q128" s="2"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+      <c r="Q129" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -4208,33 +4508,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -4261,16 +4561,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -4297,1036 +4597,1036 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>60</v>
+      <c r="A6" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>63</v>
+      <c r="A7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" ref="B25:B88" si="1">lower(substitute(C25," ",""))</f>
         <v>chakechakedistricthospital</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
         <v>pujiniphcu+</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
         <v>tundauwaphcu+</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
         <v>vitongojiphcc</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
         <v>weshaphcu+</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
         <v>kondephcu+</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
         <v>makangalephcu+</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
         <v>maziwangombephcu+</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
         <v>micheweniphcc</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
         <v>wingwiphcu+</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
         <v>kiuyumbuyuniphcu+</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
         <v>bogoaphcu+</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
         <v>kengejaphcu+</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
         <v>abdallahmzeedistricthospital</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
         <v>michenzaniphcu+</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
         <v>fundophcu+</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="1"/>
         <v>kojaniphcu+</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="1"/>
         <v>makongeniphcu+</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="1"/>
         <v>wetedistricthospital</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="1"/>
         <v>mzambarauniphcu+</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="1"/>
         <v>junguniphcu+</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="1"/>
         <v>ukunjwiphcu+</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="1"/>
         <v>uondwephcu+</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="1"/>
         <v>chwakaphcu+</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="1"/>
         <v>mweraphcu+</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="1"/>
         <v>ungujaukuuphcu+</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="1"/>
         <v>uziniphcu+</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="1"/>
         <v>uroaphcu+</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="1"/>
         <v>kivungedistricthospital</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B54" t="str">
         <f t="shared" si="1"/>
         <v>matemwephcu+</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B55" t="str">
         <f t="shared" si="1"/>
         <v>nungwiphcu+</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B56" t="str">
         <f t="shared" si="1"/>
         <v>pwanimchanganiphcu+</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B57" t="str">
         <f t="shared" si="1"/>
         <v>tumbatugomaniphcu+</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B58" t="str">
         <f t="shared" si="1"/>
         <v>kendwaphcu+</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B59" t="str">
         <f t="shared" si="1"/>
         <v>bumbwinimisufiniphcu+</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B60" t="str">
         <f t="shared" si="1"/>
         <v>dongevijibweniphcu+</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B61" t="str">
         <f t="shared" si="1"/>
         <v>kiongwephcu</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="1"/>
         <v>kitopephcu</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="1"/>
         <v>mahondaphcu+</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B64" t="str">
         <f t="shared" si="1"/>
@@ -5339,1069 +5639,1069 @@
         <v>215</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B65" t="str">
         <f t="shared" si="1"/>
         <v>makunduchidistricthospital</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B66" t="str">
         <f t="shared" si="1"/>
         <v>muyuniphcu+</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B67" t="str">
         <f t="shared" si="1"/>
         <v>bwejuuphcu+</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B68" t="str">
         <f t="shared" si="1"/>
         <v>chumbuniphcu+</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B69" t="str">
         <f t="shared" si="1"/>
         <v>mnazimmojahospital</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B70" t="str">
         <f t="shared" si="1"/>
         <v>mwembeladumchclinic</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B71" t="str">
         <f t="shared" si="1"/>
         <v>sebleniphcu+</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B72" t="str">
         <f t="shared" si="1"/>
         <v>chukwaniphcu+</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B73" t="str">
         <f t="shared" si="1"/>
         <v>fuoniphcu+</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B74" t="str">
         <f t="shared" si="1"/>
         <v>kombeniphcu+</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B75" t="str">
         <f t="shared" si="1"/>
         <v>mtofaaniphcu+(kinuni)</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B76" t="str">
         <f t="shared" si="1"/>
         <v>bumbwisudiphcu+</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B77" t="str">
         <f t="shared" si="1"/>
         <v>selemphcu+</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B78" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E78" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B79" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E79" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B80" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E80" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B81" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E81" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B82" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E82" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B83" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E83" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B84" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E84" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B85" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E85" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B86" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E86" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B87" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E87" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B88" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="E88" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>378</v>
+        <v>351</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>392</v>
+        <v>359</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>394</v>
+        <v>361</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>398</v>
+        <v>368</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D120" s="20" t="s">
-        <v>433</v>
+        <v>409</v>
+      </c>
+      <c r="D120" s="24" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="D121" s="20" t="s">
-        <v>438</v>
+        <v>414</v>
+      </c>
+      <c r="D121" s="24" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>443</v>
+        <v>418</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>455</v>
+        <v>427</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>456</v>
+        <v>428</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>463</v>
+        <v>436</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>465</v>
+        <v>437</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>468</v>
+        <v>441</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="D128" s="2" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C130" s="26" t="s">
-        <v>484</v>
+        <v>449</v>
+      </c>
+      <c r="C130" s="29" t="s">
+        <v>450</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C131" s="9" t="s">
-        <v>496</v>
+        <v>268</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>472</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="14" t="s">
+      <c r="A132" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="B132" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="C132" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="D132" s="31" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="B133" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="C133" s="30" t="s">
         <v>500</v>
       </c>
-      <c r="B132" s="14" t="s">
+      <c r="D133" s="31" t="s">
         <v>502</v>
-      </c>
-      <c r="C132" s="27" t="s">
-        <v>504</v>
-      </c>
-      <c r="D132" s="28" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="14" t="s">
-        <v>500</v>
-      </c>
-      <c r="B133" s="14" t="s">
-        <v>516</v>
-      </c>
-      <c r="C133" s="27" t="s">
-        <v>517</v>
-      </c>
-      <c r="D133" s="28" t="s">
-        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -6422,19 +6722,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>25</v>
@@ -6442,19 +6742,19 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5">
         <v>43580.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1"/>
     </row>

--- a/forms/app/pregnancy_outcomes.xlsx
+++ b/forms/app/pregnancy_outcomes.xlsx
@@ -1,19 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="4425" windowHeight="2115"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="survey" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="choices" sheetId="2" r:id="rId4"/>
-    <sheet state="visible" name="settings" sheetId="3" r:id="rId5"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="598">
   <si>
     <t>type</t>
   </si>
@@ -1834,52 +1842,75 @@
   <si>
     <t>data</t>
   </si>
+  <si>
+    <t>select_multiple stillbirth_location</t>
+  </si>
+  <si>
+    <t>stillbirth_location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where did stillbirth occur? </t>
+  </si>
+  <si>
+    <t>Mimba ya ${client_name} iliharibika wapi?</t>
+  </si>
+  <si>
+    <t>${date_of_pregnancy_loss}!= '' and ${miscarriage_or_stillbirth} = "stillbirth"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="10">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF1D1C1D"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
     </font>
@@ -1889,7 +1920,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1905,166 +1936,369 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
+      <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="38">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z130"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.43"/>
-    <col customWidth="1" min="2" max="2" width="23.86"/>
-    <col customWidth="1" min="3" max="3" width="287.43"/>
-    <col customWidth="1" min="4" max="4" width="44.0"/>
-    <col customWidth="1" min="6" max="6" width="29.0"/>
-    <col customWidth="1" min="11" max="11" width="21.0"/>
-    <col customWidth="1" min="20" max="20" width="23.86"/>
+    <col min="1" max="1" width="24.40625" customWidth="1"/>
+    <col min="2" max="2" width="23.86328125" customWidth="1"/>
+    <col min="3" max="3" width="287.40625" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="20" max="20" width="23.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:21" ht="13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2129,7 +2363,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:21" ht="13">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -2146,7 +2380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:21" ht="13">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -2157,7 +2391,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:21" ht="13">
       <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
@@ -2168,7 +2402,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:21" ht="13">
       <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
@@ -2179,7 +2413,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:21" ht="13">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -2190,7 +2424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:21" ht="13">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
@@ -2201,7 +2435,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:21" ht="13">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -2210,7 +2444,7 @@
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:21" ht="13">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -2221,7 +2455,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:21" ht="13">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -2235,7 +2469,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:21" ht="13">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -2246,7 +2480,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:21" ht="13">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -2257,7 +2491,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:21" ht="13">
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
@@ -2268,7 +2502,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:21" ht="13">
       <c r="A14" s="5" t="s">
         <v>21</v>
       </c>
@@ -2279,7 +2513,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:21" ht="13">
       <c r="A15" s="5" t="s">
         <v>27</v>
       </c>
@@ -2290,7 +2524,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:21" ht="13">
       <c r="A16" s="5" t="s">
         <v>21</v>
       </c>
@@ -2301,7 +2535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:26" ht="13">
       <c r="A17" s="5" t="s">
         <v>27</v>
       </c>
@@ -2312,7 +2546,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:26" ht="13">
       <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
@@ -2323,7 +2557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:26" ht="13">
       <c r="A19" s="5" t="s">
         <v>27</v>
       </c>
@@ -2334,7 +2568,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:26" ht="13">
       <c r="A20" s="5" t="s">
         <v>34</v>
       </c>
@@ -2343,7 +2577,7 @@
       </c>
       <c r="C20" s="1"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:26" ht="13">
       <c r="A21" s="5" t="s">
         <v>34</v>
       </c>
@@ -2352,7 +2586,7 @@
       </c>
       <c r="C21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:26" ht="13">
       <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
@@ -2361,7 +2595,7 @@
       </c>
       <c r="C22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:26" ht="13">
       <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
@@ -2370,7 +2604,7 @@
       </c>
       <c r="C23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:26" ht="13">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -2379,7 +2613,7 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:26" ht="13">
       <c r="A25" s="7" t="s">
         <v>45</v>
       </c>
@@ -2413,7 +2647,7 @@
       <c r="Y25" s="7"/>
       <c r="Z25" s="7"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:26" ht="13">
       <c r="A26" s="7" t="s">
         <v>45</v>
       </c>
@@ -2447,7 +2681,7 @@
       <c r="Y26" s="7"/>
       <c r="Z26" s="7"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:26" ht="13">
       <c r="A27" s="7" t="s">
         <v>45</v>
       </c>
@@ -2481,7 +2715,7 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:26" ht="13">
       <c r="A28" s="5" t="s">
         <v>45</v>
       </c>
@@ -2501,7 +2735,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:26" ht="13">
       <c r="A29" s="5" t="s">
         <v>45</v>
       </c>
@@ -2521,7 +2755,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:26" ht="13">
       <c r="A30" s="1" t="s">
         <v>45</v>
       </c>
@@ -2541,7 +2775,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:26" ht="13">
       <c r="A31" s="1" t="s">
         <v>45</v>
       </c>
@@ -2561,7 +2795,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:26" ht="13">
       <c r="A32" s="1" t="s">
         <v>45</v>
       </c>
@@ -2581,7 +2815,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:26" ht="13">
       <c r="A33" s="1" t="s">
         <v>45</v>
       </c>
@@ -2601,7 +2835,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:26" ht="13">
       <c r="A34" s="1" t="s">
         <v>45</v>
       </c>
@@ -2621,7 +2855,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:26" ht="13">
       <c r="A35" s="1" t="s">
         <v>45</v>
       </c>
@@ -2641,7 +2875,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:26" ht="13">
       <c r="A36" s="1" t="s">
         <v>45</v>
       </c>
@@ -2661,7 +2895,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:26" ht="13">
       <c r="A37" s="13" t="s">
         <v>45</v>
       </c>
@@ -2681,7 +2915,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:26" ht="13">
       <c r="A38" s="13" t="s">
         <v>45</v>
       </c>
@@ -2701,7 +2935,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:26" ht="13">
       <c r="A39" s="13" t="s">
         <v>45</v>
       </c>
@@ -2721,7 +2955,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:26" ht="13">
       <c r="A40" s="13" t="s">
         <v>45</v>
       </c>
@@ -2741,7 +2975,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:26" ht="13">
       <c r="A41" s="5" t="s">
         <v>45</v>
       </c>
@@ -2775,7 +3009,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:26" ht="13">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -2792,7 +3026,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="17">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
@@ -2809,7 +3043,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:26" ht="13">
       <c r="A43" s="1" t="s">
         <v>45</v>
       </c>
@@ -2826,7 +3060,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="17">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
@@ -2843,7 +3077,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:26" ht="13">
       <c r="A44" s="13" t="s">
         <v>80</v>
       </c>
@@ -2875,7 +3109,7 @@
       <c r="Y44" s="19"/>
       <c r="Z44" s="19"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:26" ht="13">
       <c r="A45" s="13" t="s">
         <v>81</v>
       </c>
@@ -2907,7 +3141,7 @@
       <c r="Y45" s="19"/>
       <c r="Z45" s="19"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:26" ht="13">
       <c r="A46" s="19" t="s">
         <v>82</v>
       </c>
@@ -2936,7 +3170,7 @@
       <c r="R46" s="19"/>
       <c r="S46" s="19"/>
     </row>
-    <row r="47" ht="18.75" customHeight="1">
+    <row r="47" spans="1:26" ht="18.75" customHeight="1">
       <c r="A47" s="19" t="s">
         <v>86</v>
       </c>
@@ -2965,7 +3199,7 @@
       <c r="R47" s="19"/>
       <c r="S47" s="19"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:26" ht="13">
       <c r="A48" s="19" t="s">
         <v>90</v>
       </c>
@@ -2990,7 +3224,7 @@
       <c r="R48" s="19"/>
       <c r="S48" s="19"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:17" ht="13">
       <c r="A49" s="1" t="s">
         <v>21</v>
       </c>
@@ -3007,7 +3241,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:17" ht="13">
       <c r="A50" s="1" t="s">
         <v>86</v>
       </c>
@@ -3021,7 +3255,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:17" ht="13">
       <c r="A51" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,7 +3269,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:17" ht="13">
       <c r="A52" s="1" t="s">
         <v>86</v>
       </c>
@@ -3049,7 +3283,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:17" ht="13">
       <c r="A53" s="3" t="s">
         <v>34</v>
       </c>
@@ -3057,7 +3291,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:17" ht="13">
       <c r="A54" s="3" t="s">
         <v>21</v>
       </c>
@@ -3074,7 +3308,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:17" ht="13">
       <c r="A55" s="3" t="s">
         <v>107</v>
       </c>
@@ -3091,7 +3325,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:17" ht="13">
       <c r="A56" s="3" t="s">
         <v>112</v>
       </c>
@@ -3120,7 +3354,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:17" ht="13">
       <c r="A57" s="3" t="s">
         <v>86</v>
       </c>
@@ -3138,7 +3372,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:17" ht="13">
       <c r="A58" s="3" t="s">
         <v>112</v>
       </c>
@@ -3158,7 +3392,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:17" ht="13">
       <c r="A59" s="3" t="s">
         <v>45</v>
       </c>
@@ -3166,299 +3400,297 @@
         <v>127</v>
       </c>
       <c r="C59" s="3"/>
-      <c r="L59" s="3" t="s">
+      <c r="L59" s="28" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
+    <row r="60" spans="1:17" ht="13">
+      <c r="A60" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="B60" s="28" t="s">
+        <v>594</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>595</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>596</v>
+      </c>
+      <c r="E60" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="F60" s="28" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="13">
+      <c r="A61" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B61" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C60" s="3"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="1:17" ht="13">
+      <c r="A62" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B62" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D62" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F61" s="24" t="s">
+      <c r="F62" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G62" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="1:17" ht="13">
+      <c r="A63" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B63" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D63" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>140</v>
-      </c>
+      <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="Q63" s="3"/>
     </row>
-    <row r="64">
-      <c r="A64" s="27" t="s">
+    <row r="64" spans="1:17" ht="13">
+      <c r="A64" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G64" s="3"/>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="1:26" ht="13">
+      <c r="A65" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B65" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C64" s="27" t="s">
+      <c r="C65" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="D65" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="E65" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="F64" s="8" t="s">
+      <c r="F65" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="G64" s="15"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="15"/>
-      <c r="R64" s="1"/>
-      <c r="S64" s="1"/>
-      <c r="T64" s="1"/>
-      <c r="U64" s="1"/>
-      <c r="V64" s="1"/>
-      <c r="W64" s="1"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="1"/>
-      <c r="Z64" s="1"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="s">
+      <c r="G65" s="15"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="15"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
+    </row>
+    <row r="66" spans="1:26" ht="13">
+      <c r="A66" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G65" s="3"/>
-      <c r="M65" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G66" s="3"/>
       <c r="M66" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="1:26" ht="13">
+      <c r="A67" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G67" s="3"/>
+      <c r="M67" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="27" t="s">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="1:26" ht="13">
+      <c r="A68" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B68" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C67" s="27" t="s">
+      <c r="C68" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="D67" s="13" t="s">
+      <c r="D68" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E67" s="13" t="s">
+      <c r="E68" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F68" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="G67" s="15"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="15"/>
-      <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="1"/>
-      <c r="V67" s="1"/>
-      <c r="W67" s="1"/>
-      <c r="X67" s="1"/>
-      <c r="Y67" s="1"/>
-      <c r="Z67" s="1"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="s">
+      <c r="G68" s="15"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="15"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+    </row>
+    <row r="69" spans="1:26" ht="13">
+      <c r="A69" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B69" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F69" s="24" t="s">
-        <v>116</v>
-      </c>
+      <c r="C69" s="3"/>
+      <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="Q69" s="3"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:26" ht="13">
       <c r="A70" s="3" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
+      </c>
+      <c r="F70" s="24" t="s">
+        <v>116</v>
       </c>
       <c r="G70" s="3"/>
       <c r="Q70" s="3"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:26" ht="13">
       <c r="A71" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="G71" s="3"/>
       <c r="Q71" s="3"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:26" ht="13">
       <c r="A72" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>111</v>
@@ -3469,91 +3701,93 @@
       <c r="G72" s="3"/>
       <c r="Q72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:26" ht="13">
       <c r="A73" s="3" t="s">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="G73" s="3"/>
       <c r="Q73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:26" ht="13">
       <c r="A74" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G74" s="3"/>
       <c r="Q74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:26" ht="13">
       <c r="A75" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G75" s="3"/>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="1:26" ht="13">
+      <c r="A76" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B76" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="L75" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="C76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
+      <c r="L76" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="Q76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:26" ht="13">
       <c r="A77" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>111</v>
@@ -3562,18 +3796,18 @@
       <c r="G77" s="3"/>
       <c r="Q77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:26" ht="13">
       <c r="A78" s="3" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>111</v>
@@ -3582,587 +3816,599 @@
       <c r="G78" s="3"/>
       <c r="Q78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:26" ht="13">
       <c r="A79" s="3" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
-      <c r="I79" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="J79" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="K79" s="28" t="s">
-        <v>202</v>
-      </c>
       <c r="Q79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:26" ht="13">
       <c r="A80" s="3" t="s">
-        <v>34</v>
+        <v>196</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C80" s="3"/>
+        <v>197</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
+      <c r="I80" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="J80" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="K80" s="28" t="s">
+        <v>202</v>
+      </c>
       <c r="Q80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:17" ht="13">
       <c r="A81" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="1:17" ht="13">
+      <c r="A82" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F81" s="24" t="s">
+      <c r="F82" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G82" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="3" t="s">
+    <row r="83" spans="1:17" ht="13">
+      <c r="A83" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B83" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="84">
+    </row>
+    <row r="84" spans="1:17" ht="13">
       <c r="A84" s="3" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>214</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="13">
       <c r="A85" s="3" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F85" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="13">
+      <c r="A86" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F86" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="I85" s="3" t="s">
+      <c r="I86" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="J85" s="3" t="s">
+      <c r="J86" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="K85" s="3" t="s">
+      <c r="K86" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="3" t="s">
+    <row r="87" spans="1:17" ht="13">
+      <c r="A87" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B87" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="3" t="s">
+    <row r="88" spans="1:17" ht="13">
+      <c r="A88" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B88" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="L87" s="3" t="s">
+      <c r="L88" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89">
+    <row r="89" spans="1:17" ht="13">
       <c r="A89" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G89" s="3"/>
       <c r="L89" s="3"/>
       <c r="Q89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:17" ht="13">
       <c r="A90" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="1:17" ht="13">
+      <c r="A91" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B91" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D91" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F91" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="G91" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="L90" s="3"/>
-      <c r="Q90" s="3" t="s">
+      <c r="L91" s="3"/>
+      <c r="Q91" s="3" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="3" t="s">
+    <row r="92" spans="1:17" ht="13">
+      <c r="A92" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B92" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D92" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E92" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="I92" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="J92" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="K92" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="s">
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="1:17" ht="13">
+      <c r="A93" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B93" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="1:17" ht="13">
+      <c r="A94" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B94" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="L93" s="3" t="s">
+      <c r="L94" s="3" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
+    <row r="95" spans="1:17" ht="13">
+      <c r="A95" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B95" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C95" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D95" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F95" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G95" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C95" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="Q95" s="3"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:17" ht="13">
       <c r="A96" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C96" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="1:21" ht="13">
+      <c r="A97" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C96" s="28" t="s">
+      <c r="C97" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F97" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="1:21" ht="13">
+      <c r="A98" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B98" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D98" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="G98" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="Q97" s="3" t="s">
+      <c r="Q98" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="T97" s="29" t="s">
+      <c r="T98" s="29" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="7" t="s">
+    <row r="99" spans="1:21" ht="13">
+      <c r="A99" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B99" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C99" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="D98" s="13" t="s">
+      <c r="D99" s="13" t="s">
         <v>268</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="B99" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="D99" s="13" t="s">
-        <v>271</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:21" ht="13">
       <c r="A100" s="30" t="s">
         <v>141</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:21" ht="13">
       <c r="A101" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="B101" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" ht="13">
+      <c r="A102" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B101" s="30" t="s">
+      <c r="B102" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7"/>
-      <c r="I101" s="7"/>
-      <c r="J101" s="7"/>
-      <c r="K101" s="7"/>
-      <c r="L101" s="8" t="s">
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="7"/>
+      <c r="L102" s="8" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
+    <row r="103" spans="1:21" ht="13">
+      <c r="A103" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B103" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C103" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E103" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="27" t="s">
+    <row r="104" spans="1:21" ht="13">
+      <c r="A104" s="27" t="s">
         <v>279</v>
       </c>
-      <c r="B103" s="27" t="s">
+      <c r="B104" s="27" t="s">
         <v>280</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C104" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D104" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E103" s="13" t="s">
+      <c r="E104" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="L103" s="3"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L104" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="105">
+      <c r="L104" s="3"/>
+    </row>
+    <row r="105" spans="1:21" ht="13">
       <c r="A105" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" ht="13">
+      <c r="A106" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="L105" s="3" t="s">
+      <c r="L106" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="U105" s="3" t="s">
+      <c r="U106" s="3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="3" t="s">
+    <row r="107" spans="1:21" ht="13">
+      <c r="A107" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B107" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C107" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="3" t="s">
+    <row r="108" spans="1:21" ht="13">
+      <c r="A108" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B108" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="L107" s="3" t="s">
+      <c r="L108" s="3" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="3" t="s">
+    <row r="109" spans="1:21" ht="13">
+      <c r="A109" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B109" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C109" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="3" t="s">
+    <row r="110" spans="1:21" ht="13">
+      <c r="A110" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B110" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C110" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="L109" s="3" t="s">
+      <c r="L110" s="3" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="3" t="s">
+    <row r="111" spans="1:21" ht="13">
+      <c r="A111" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B111" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C111" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="3" t="s">
+    <row r="112" spans="1:21" ht="13">
+      <c r="A112" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B112" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="L111" s="3" t="s">
+      <c r="L112" s="3" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="113">
+    <row r="113" spans="1:26" ht="13">
       <c r="A113" s="3" t="s">
         <v>34</v>
       </c>
@@ -4170,7 +4416,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:26" ht="13">
       <c r="A114" s="3" t="s">
         <v>34</v>
       </c>
@@ -4178,63 +4424,37 @@
         <v>41</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:26" ht="13">
       <c r="A115" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26" ht="13">
+      <c r="A116" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B116" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C116" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="L115" s="3" t="s">
+      <c r="L116" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="P115" s="3" t="s">
+      <c r="P116" s="3" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="B116" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7"/>
-      <c r="J116" s="7"/>
-      <c r="K116" s="7"/>
-      <c r="L116" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="M116" s="7"/>
-      <c r="N116" s="7"/>
-      <c r="O116" s="7"/>
-      <c r="P116" s="7"/>
-      <c r="Q116" s="7"/>
-      <c r="R116" s="7"/>
-      <c r="S116" s="7"/>
-      <c r="T116" s="7"/>
-      <c r="U116" s="7"/>
-      <c r="V116" s="7"/>
-      <c r="W116" s="7"/>
-      <c r="X116" s="7"/>
-      <c r="Y116" s="7"/>
-      <c r="Z116" s="7"/>
-    </row>
-    <row r="117">
+    <row r="117" spans="1:26" ht="13">
       <c r="A117" s="30" t="s">
         <v>45</v>
       </c>
       <c r="B117" s="30" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
@@ -4246,7 +4466,7 @@
       <c r="J117" s="7"/>
       <c r="K117" s="7"/>
       <c r="L117" s="7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M117" s="7"/>
       <c r="N117" s="7"/>
@@ -4263,12 +4483,12 @@
       <c r="Y117" s="7"/>
       <c r="Z117" s="7"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:26" ht="13">
       <c r="A118" s="30" t="s">
         <v>45</v>
       </c>
       <c r="B118" s="30" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
@@ -4280,7 +4500,7 @@
       <c r="J118" s="7"/>
       <c r="K118" s="7"/>
       <c r="L118" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="M118" s="7"/>
       <c r="N118" s="7"/>
@@ -4297,139 +4517,151 @@
       <c r="Y118" s="7"/>
       <c r="Z118" s="7"/>
     </row>
-    <row r="119">
-      <c r="A119" s="3" t="s">
+    <row r="119" spans="1:26" ht="13">
+      <c r="A119" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="B119" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="C119" s="7"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="7"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="7"/>
+      <c r="J119" s="7"/>
+      <c r="K119" s="7"/>
+      <c r="L119" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="M119" s="7"/>
+      <c r="N119" s="7"/>
+      <c r="O119" s="7"/>
+      <c r="P119" s="7"/>
+      <c r="Q119" s="7"/>
+      <c r="R119" s="7"/>
+      <c r="S119" s="7"/>
+      <c r="T119" s="7"/>
+      <c r="U119" s="7"/>
+      <c r="V119" s="7"/>
+      <c r="W119" s="7"/>
+      <c r="X119" s="7"/>
+      <c r="Y119" s="7"/>
+      <c r="Z119" s="7"/>
+    </row>
+    <row r="120" spans="1:26" ht="13">
+      <c r="A120" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B120" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="3" t="s">
+    <row r="121" spans="1:26" ht="13">
+      <c r="A121" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B121" s="3" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="3" t="s">
+    <row r="122" spans="1:26" ht="13">
+      <c r="A122" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B122" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C122" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D121" s="31" t="s">
+      <c r="D122" s="31" t="s">
         <v>304</v>
       </c>
-      <c r="F121" s="3" t="s">
+      <c r="F122" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="G121" s="3"/>
-      <c r="Q121" s="3"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D122" s="32" t="s">
-        <v>308</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F122" s="3"/>
       <c r="G122" s="3"/>
       <c r="Q122" s="3"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:26" ht="13">
       <c r="A123" s="3" t="s">
-        <v>309</v>
+        <v>172</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
+      </c>
+      <c r="D123" s="32" t="s">
+        <v>308</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F123" s="3" t="s">
-        <v>313</v>
-      </c>
+      <c r="F123" s="3"/>
       <c r="G123" s="3"/>
       <c r="Q123" s="3"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:26" ht="13">
       <c r="A124" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G124" s="3"/>
       <c r="Q124" s="3"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:26" ht="13">
       <c r="A125" s="3" t="s">
-        <v>172</v>
+        <v>314</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="G125" s="3"/>
       <c r="Q125" s="3"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:26" ht="13">
       <c r="A126" s="3" t="s">
         <v>172</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>111</v>
@@ -4440,82 +4672,105 @@
       <c r="G126" s="3"/>
       <c r="Q126" s="3"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:26" ht="13">
       <c r="A127" s="3" t="s">
-        <v>325</v>
+        <v>172</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="G127" s="3"/>
       <c r="Q127" s="3"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:26" ht="13">
       <c r="A128" s="3" t="s">
-        <v>172</v>
+        <v>325</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>111</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="G128" s="3"/>
       <c r="Q128" s="3"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:17" ht="13">
       <c r="A129" s="3" t="s">
-        <v>34</v>
+        <v>172</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
-      <c r="F129" s="3"/>
+        <v>330</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>313</v>
+      </c>
       <c r="G129" s="3"/>
       <c r="Q129" s="3"/>
     </row>
+    <row r="130" spans="1:17" ht="13">
+      <c r="A130" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+      <c r="Q130" s="3"/>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z136"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.0"/>
-    <col customWidth="1" min="2" max="2" width="22.86"/>
-    <col customWidth="1" min="3" max="3" width="49.57"/>
-    <col customWidth="1" min="4" max="4" width="82.29"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="22.86328125" customWidth="1"/>
+    <col min="3" max="3" width="49.54296875" customWidth="1"/>
+    <col min="4" max="4" width="82.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>333</v>
       </c>
@@ -4532,7 +4787,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>334</v>
       </c>
@@ -4568,7 +4823,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>334</v>
       </c>
@@ -4604,7 +4859,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>340</v>
       </c>
@@ -4618,7 +4873,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>340</v>
       </c>
@@ -4632,7 +4887,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26">
       <c r="A6" s="33" t="s">
         <v>39</v>
       </c>
@@ -4646,7 +4901,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26">
       <c r="A7" s="33" t="s">
         <v>39</v>
       </c>
@@ -4660,7 +4915,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" ht="13">
       <c r="A8" s="3" t="s">
         <v>133</v>
       </c>
@@ -4674,7 +4929,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" ht="13">
       <c r="A9" s="3" t="s">
         <v>133</v>
       </c>
@@ -4688,7 +4943,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" ht="13">
       <c r="A10" s="3" t="s">
         <v>133</v>
       </c>
@@ -4702,7 +4957,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26" ht="13">
       <c r="A11" s="3" t="s">
         <v>137</v>
       </c>
@@ -4716,7 +4971,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" ht="13">
       <c r="A12" s="3" t="s">
         <v>137</v>
       </c>
@@ -4730,7 +4985,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" ht="13">
       <c r="A13" s="3" t="s">
         <v>137</v>
       </c>
@@ -4744,7 +4999,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" ht="13">
       <c r="A14" s="3" t="s">
         <v>147</v>
       </c>
@@ -4761,7 +5016,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:26" ht="13">
       <c r="A15" s="3" t="s">
         <v>147</v>
       </c>
@@ -4778,7 +5033,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26" ht="13">
       <c r="A16" s="3" t="s">
         <v>147</v>
       </c>
@@ -4795,7 +5050,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" ht="13">
       <c r="A17" s="3" t="s">
         <v>147</v>
       </c>
@@ -4812,7 +5067,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" ht="13">
       <c r="A18" s="3" t="s">
         <v>147</v>
       </c>
@@ -4829,7 +5084,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" ht="13">
       <c r="A19" s="3" t="s">
         <v>147</v>
       </c>
@@ -4846,7 +5101,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" ht="13">
       <c r="A20" s="3" t="s">
         <v>147</v>
       </c>
@@ -4863,7 +5118,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" ht="13">
       <c r="A21" s="3" t="s">
         <v>147</v>
       </c>
@@ -4880,7 +5135,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" ht="13">
       <c r="A22" s="3" t="s">
         <v>147</v>
       </c>
@@ -4897,7 +5152,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" ht="13">
       <c r="A23" s="3" t="s">
         <v>147</v>
       </c>
@@ -4914,7 +5169,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" ht="13">
       <c r="A24" s="3" t="s">
         <v>147</v>
       </c>
@@ -4931,12 +5186,12 @@
         <v>364</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" ht="13">
       <c r="A25" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" ref="B25:B88" si="1">lower(substitute(C25," ",""))</f>
+        <f t="shared" ref="B25:B88" si="0">LOWER(SUBSTITUTE(C25," ",""))</f>
         <v>chakechakedistricthospital</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -4949,12 +5204,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" ht="13">
       <c r="A26" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>pujiniphcu+</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -4967,12 +5222,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" ht="13">
       <c r="A27" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>tundauwaphcu+</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -4985,12 +5240,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" ht="13">
       <c r="A28" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>vitongojiphcc</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -5003,12 +5258,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5" ht="13">
       <c r="A29" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>weshaphcu+</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -5021,12 +5276,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5" ht="13">
       <c r="A30" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kondephcu+</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -5039,12 +5294,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5" ht="13">
       <c r="A31" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B31" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>makangalephcu+</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -5057,12 +5312,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5" ht="13">
       <c r="A32" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>maziwangombephcu+</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -5075,12 +5330,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5" ht="13">
       <c r="A33" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>micheweniphcc</v>
       </c>
       <c r="C33" s="3" t="s">
@@ -5093,12 +5348,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:5" ht="13">
       <c r="A34" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>wingwiphcu+</v>
       </c>
       <c r="C34" s="3" t="s">
@@ -5111,12 +5366,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:5" ht="13">
       <c r="A35" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kiuyumbuyuniphcu+</v>
       </c>
       <c r="C35" s="3" t="s">
@@ -5129,12 +5384,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" ht="13">
       <c r="A36" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B36" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>bogoaphcu+</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -5147,12 +5402,12 @@
         <v>394</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" ht="13">
       <c r="A37" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B37" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kengejaphcu+</v>
       </c>
       <c r="C37" s="3" t="s">
@@ -5165,12 +5420,12 @@
         <v>394</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:5" ht="13">
       <c r="A38" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B38" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>abdallahmzeedistricthospital</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -5183,12 +5438,12 @@
         <v>394</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" ht="13">
       <c r="A39" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B39" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>michenzaniphcu+</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -5201,12 +5456,12 @@
         <v>394</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" ht="13">
       <c r="A40" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B40" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>fundophcu+</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -5219,12 +5474,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" ht="13">
       <c r="A41" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B41" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kojaniphcu+</v>
       </c>
       <c r="C41" s="3" t="s">
@@ -5237,12 +5492,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" ht="13">
       <c r="A42" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B42" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>makongeniphcu+</v>
       </c>
       <c r="C42" s="3" t="s">
@@ -5255,12 +5510,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" ht="13">
       <c r="A43" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>wetedistricthospital</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -5273,12 +5528,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" ht="13">
       <c r="A44" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B44" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mzambarauniphcu+</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -5291,12 +5546,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:5" ht="13">
       <c r="A45" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>junguniphcu+</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -5309,12 +5564,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" ht="13">
       <c r="A46" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B46" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ukunjwiphcu+</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -5327,12 +5582,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" ht="13">
       <c r="A47" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B47" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>uondwephcu+</v>
       </c>
       <c r="C47" s="3" t="s">
@@ -5345,12 +5600,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:5" ht="13">
       <c r="A48" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B48" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>chwakaphcu+</v>
       </c>
       <c r="C48" s="3" t="s">
@@ -5363,12 +5618,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:5" ht="13">
       <c r="A49" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B49" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mweraphcu+</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -5381,12 +5636,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:5" ht="13">
       <c r="A50" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B50" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ungujaukuuphcu+</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -5399,12 +5654,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:5" ht="13">
       <c r="A51" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B51" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>uziniphcu+</v>
       </c>
       <c r="C51" s="3" t="s">
@@ -5417,12 +5672,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:5" ht="13">
       <c r="A52" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B52" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>uroaphcu+</v>
       </c>
       <c r="C52" s="3" t="s">
@@ -5435,12 +5690,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:5" ht="13">
       <c r="A53" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B53" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kivungedistricthospital</v>
       </c>
       <c r="C53" s="3" t="s">
@@ -5453,12 +5708,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:5" ht="13">
       <c r="A54" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B54" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>matemwephcu+</v>
       </c>
       <c r="C54" s="3" t="s">
@@ -5471,12 +5726,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:5" ht="13">
       <c r="A55" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B55" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>nungwiphcu+</v>
       </c>
       <c r="C55" s="3" t="s">
@@ -5489,12 +5744,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:5" ht="13">
       <c r="A56" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>pwanimchanganiphcu+</v>
       </c>
       <c r="C56" s="3" t="s">
@@ -5507,12 +5762,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:5" ht="13">
       <c r="A57" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>tumbatugomaniphcu+</v>
       </c>
       <c r="C57" s="3" t="s">
@@ -5525,12 +5780,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:5" ht="13">
       <c r="A58" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B58" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kendwaphcu+</v>
       </c>
       <c r="C58" s="3" t="s">
@@ -5543,12 +5798,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:5" ht="13">
       <c r="A59" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B59" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>bumbwinimisufiniphcu+</v>
       </c>
       <c r="C59" s="3" t="s">
@@ -5561,12 +5816,12 @@
         <v>372</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:5" ht="13">
       <c r="A60" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B60" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>dongevijibweniphcu+</v>
       </c>
       <c r="C60" s="3" t="s">
@@ -5579,12 +5834,12 @@
         <v>372</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:5" ht="13">
       <c r="A61" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B61" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kiongwephcu</v>
       </c>
       <c r="C61" s="3" t="s">
@@ -5597,12 +5852,12 @@
         <v>372</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:5" ht="13">
       <c r="A62" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B62" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kitopephcu</v>
       </c>
       <c r="C62" s="3" t="s">
@@ -5615,12 +5870,12 @@
         <v>372</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:5" ht="13">
       <c r="A63" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B63" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mahondaphcu+</v>
       </c>
       <c r="C63" s="3" t="s">
@@ -5633,12 +5888,12 @@
         <v>372</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:5" ht="13">
       <c r="A64" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B64" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>jambianiphcu+</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -5651,12 +5906,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:5" ht="13">
       <c r="A65" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B65" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>makunduchidistricthospital</v>
       </c>
       <c r="C65" s="3" t="s">
@@ -5669,12 +5924,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:5" ht="13">
       <c r="A66" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>muyuniphcu+</v>
       </c>
       <c r="C66" s="3" t="s">
@@ -5687,12 +5942,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:5" ht="13">
       <c r="A67" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B67" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>bwejuuphcu+</v>
       </c>
       <c r="C67" s="3" t="s">
@@ -5705,12 +5960,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:5" ht="13">
       <c r="A68" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B68" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>chumbuniphcu+</v>
       </c>
       <c r="C68" s="3" t="s">
@@ -5723,12 +5978,12 @@
         <v>387</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:5" ht="13">
       <c r="A69" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B69" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mnazimmojahospital</v>
       </c>
       <c r="C69" s="3" t="s">
@@ -5741,12 +5996,12 @@
         <v>387</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:5" ht="13">
       <c r="A70" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B70" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mwembeladumchclinic</v>
       </c>
       <c r="C70" s="3" t="s">
@@ -5759,12 +6014,12 @@
         <v>387</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:5" ht="13">
       <c r="A71" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B71" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>sebleniphcu+</v>
       </c>
       <c r="C71" s="3" t="s">
@@ -5777,12 +6032,12 @@
         <v>387</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:5" ht="13">
       <c r="A72" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>chukwaniphcu+</v>
       </c>
       <c r="C72" s="3" t="s">
@@ -5795,12 +6050,12 @@
         <v>384</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:5" ht="13">
       <c r="A73" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B73" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>fuoniphcu+</v>
       </c>
       <c r="C73" s="3" t="s">
@@ -5813,12 +6068,12 @@
         <v>384</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:5" ht="13">
       <c r="A74" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kombeniphcu+</v>
       </c>
       <c r="C74" s="3" t="s">
@@ -5831,12 +6086,12 @@
         <v>384</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:5" ht="13">
       <c r="A75" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B75" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mtofaaniphcu+(kinuni)</v>
       </c>
       <c r="C75" s="3" t="s">
@@ -5849,12 +6104,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:5" ht="13">
       <c r="A76" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B76" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>bumbwisudiphcu+</v>
       </c>
       <c r="C76" s="3" t="s">
@@ -5867,12 +6122,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:5" ht="13">
       <c r="A77" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>selemphcu+</v>
       </c>
       <c r="C77" s="3" t="s">
@@ -5885,12 +6140,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:5" ht="13">
       <c r="A78" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B78" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C78" s="3" t="s">
@@ -5903,12 +6158,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:5" ht="13">
       <c r="A79" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B79" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C79" s="3" t="s">
@@ -5921,12 +6176,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:5" ht="13">
       <c r="A80" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B80" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C80" s="3" t="s">
@@ -5939,12 +6194,12 @@
         <v>394</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:5" ht="13">
       <c r="A81" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B81" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C81" s="3" t="s">
@@ -5957,12 +6212,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:5" ht="13">
       <c r="A82" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B82" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C82" s="3" t="s">
@@ -5975,12 +6230,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:5" ht="13">
       <c r="A83" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B83" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C83" s="3" t="s">
@@ -5993,12 +6248,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:5" ht="13">
       <c r="A84" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C84" s="3" t="s">
@@ -6011,12 +6266,12 @@
         <v>372</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:5" ht="13">
       <c r="A85" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B85" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C85" s="3" t="s">
@@ -6029,12 +6284,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:5" ht="13">
       <c r="A86" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C86" s="3" t="s">
@@ -6047,12 +6302,12 @@
         <v>387</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:5" ht="13">
       <c r="A87" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B87" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C87" s="3" t="s">
@@ -6065,12 +6320,12 @@
         <v>384</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:5" ht="13">
       <c r="A88" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B88" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C88" s="3" t="s">
@@ -6083,7 +6338,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:5" ht="13">
       <c r="A89" s="3" t="s">
         <v>458</v>
       </c>
@@ -6097,7 +6352,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:5" ht="13">
       <c r="A90" s="3" t="s">
         <v>458</v>
       </c>
@@ -6111,7 +6366,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:5" ht="13">
       <c r="A91" s="3" t="s">
         <v>458</v>
       </c>
@@ -6125,7 +6380,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:5" ht="13">
       <c r="A92" s="3" t="s">
         <v>168</v>
       </c>
@@ -6139,7 +6394,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:5" ht="13">
       <c r="A93" s="3" t="s">
         <v>168</v>
       </c>
@@ -6153,7 +6408,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:5" ht="13">
       <c r="A94" s="3" t="s">
         <v>168</v>
       </c>
@@ -6167,7 +6422,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:5" ht="13">
       <c r="A95" s="3" t="s">
         <v>168</v>
       </c>
@@ -6181,7 +6436,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:5" ht="13">
       <c r="A96" s="3" t="s">
         <v>168</v>
       </c>
@@ -6195,7 +6450,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:4" ht="13">
       <c r="A97" s="3" t="s">
         <v>190</v>
       </c>
@@ -6209,7 +6464,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:4" ht="13">
       <c r="A98" s="3" t="s">
         <v>190</v>
       </c>
@@ -6223,7 +6478,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:4" ht="13">
       <c r="A99" s="3" t="s">
         <v>197</v>
       </c>
@@ -6237,7 +6492,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:4" ht="13">
       <c r="A100" s="3" t="s">
         <v>197</v>
       </c>
@@ -6251,7 +6506,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:4" ht="13">
       <c r="A101" s="3" t="s">
         <v>197</v>
       </c>
@@ -6265,7 +6520,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:4" ht="13">
       <c r="A102" s="3" t="s">
         <v>197</v>
       </c>
@@ -6279,7 +6534,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:4" ht="13">
       <c r="A103" s="3" t="s">
         <v>197</v>
       </c>
@@ -6293,7 +6548,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:4" ht="13">
       <c r="A104" s="3" t="s">
         <v>197</v>
       </c>
@@ -6307,7 +6562,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:4" ht="13">
       <c r="A105" s="3" t="s">
         <v>197</v>
       </c>
@@ -6321,7 +6576,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:4" ht="13">
       <c r="A106" s="3" t="s">
         <v>197</v>
       </c>
@@ -6335,7 +6590,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:4" ht="13">
       <c r="A107" s="3" t="s">
         <v>197</v>
       </c>
@@ -6349,7 +6604,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:4" ht="13">
       <c r="A108" s="3" t="s">
         <v>197</v>
       </c>
@@ -6363,7 +6618,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:4" ht="13">
       <c r="A109" s="3" t="s">
         <v>197</v>
       </c>
@@ -6377,7 +6632,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:4" ht="13">
       <c r="A110" s="3" t="s">
         <v>514</v>
       </c>
@@ -6391,7 +6646,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:4" ht="13">
       <c r="A111" s="3" t="s">
         <v>514</v>
       </c>
@@ -6405,7 +6660,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:4" ht="13">
       <c r="A112" s="3" t="s">
         <v>514</v>
       </c>
@@ -6419,7 +6674,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:4" ht="13">
       <c r="A113" s="3" t="s">
         <v>524</v>
       </c>
@@ -6433,7 +6688,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:4" ht="13">
       <c r="A114" s="3" t="s">
         <v>524</v>
       </c>
@@ -6447,7 +6702,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:4" ht="13">
       <c r="A115" s="3" t="s">
         <v>524</v>
       </c>
@@ -6461,7 +6716,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:4" ht="13">
       <c r="A116" s="3" t="s">
         <v>524</v>
       </c>
@@ -6475,7 +6730,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:4" ht="13">
       <c r="A117" s="3" t="s">
         <v>524</v>
       </c>
@@ -6489,7 +6744,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:4" ht="13">
       <c r="A118" s="3" t="s">
         <v>538</v>
       </c>
@@ -6503,7 +6758,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:4" ht="13">
       <c r="A119" s="3" t="s">
         <v>538</v>
       </c>
@@ -6517,7 +6772,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:4" ht="13">
       <c r="A120" s="3" t="s">
         <v>538</v>
       </c>
@@ -6531,7 +6786,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:4" ht="13">
       <c r="A121" s="3" t="s">
         <v>538</v>
       </c>
@@ -6545,7 +6800,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:4" ht="13">
       <c r="A122" s="3" t="s">
         <v>538</v>
       </c>
@@ -6559,7 +6814,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:4" ht="13">
       <c r="A123" s="3" t="s">
         <v>326</v>
       </c>
@@ -6573,7 +6828,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:4" ht="13">
       <c r="A124" s="3" t="s">
         <v>326</v>
       </c>
@@ -6587,7 +6842,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:4" ht="13">
       <c r="A125" s="3" t="s">
         <v>326</v>
       </c>
@@ -6601,7 +6856,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:4" ht="13">
       <c r="A126" s="3" t="s">
         <v>326</v>
       </c>
@@ -6615,7 +6870,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:4" ht="13">
       <c r="A127" s="3" t="s">
         <v>326</v>
       </c>
@@ -6629,7 +6884,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:4" ht="13">
       <c r="A128" s="3" t="s">
         <v>326</v>
       </c>
@@ -6643,7 +6898,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:4" ht="13">
       <c r="A129" s="3" t="s">
         <v>326</v>
       </c>
@@ -6657,7 +6912,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:4" ht="13">
       <c r="A130" s="3" t="s">
         <v>108</v>
       </c>
@@ -6671,7 +6926,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:4" ht="13">
       <c r="A131" s="3" t="s">
         <v>108</v>
       </c>
@@ -6685,7 +6940,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:4" ht="13">
       <c r="A132" s="13" t="s">
         <v>576</v>
       </c>
@@ -6699,7 +6954,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:4" ht="13">
       <c r="A133" s="13" t="s">
         <v>576</v>
       </c>
@@ -6713,23 +6968,66 @@
         <v>582</v>
       </c>
     </row>
+    <row r="134" spans="1:4" ht="13">
+      <c r="A134" s="28" t="s">
+        <v>594</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="13">
+      <c r="A135" s="28" t="s">
+        <v>594</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="13">
+      <c r="A136" s="28" t="s">
+        <v>594</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>361</v>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="31.86"/>
-    <col customWidth="1" min="2" max="2" width="25.0"/>
+    <col min="1" max="1" width="31.86328125" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>583</v>
       </c>
@@ -6749,7 +7047,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>589</v>
       </c>
@@ -6757,7 +7055,7 @@
         <v>590</v>
       </c>
       <c r="C2" s="37">
-        <v>43580.0</v>
+        <v>43580</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>591</v>
@@ -6768,6 +7066,6 @@
       <c r="F2" s="1"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>